--- a/public/data/main-source-v4_operational_elite_enhanced.xlsx
+++ b/public/data/main-source-v4_operational_elite_enhanced.xlsx
@@ -837,22 +837,22 @@
         <v>John Carter</v>
       </c>
       <c r="C2" t="str">
-        <v>1240 W 6th St, Cleveland, OH 44113</v>
+        <v>220 Demo Street, Cleveland, OH 44113</v>
       </c>
       <c r="D2" t="str">
-        <v>206-667-3424</v>
+        <v>206-555-0102</v>
       </c>
       <c r="E2" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="F2" t="str">
         <v>Huntington</v>
       </c>
       <c r="G2">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H2">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I2" t="str">
         <v>CDL Summary</v>
@@ -861,7 +861,7 @@
         <v>VALID</v>
       </c>
       <c r="K2" t="str">
-        <v>OH1668243</v>
+        <v>OH0000075</v>
       </c>
       <c r="L2">
         <v>46621</v>
@@ -888,7 +888,7 @@
         <v>M</v>
       </c>
       <c r="U2">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V2" t="str">
         <v>DRV-001.png</v>
@@ -897,10 +897,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X2" t="str">
-        <v>jcarter@yahoo.com</v>
+        <v>jcarter@example.com</v>
       </c>
       <c r="Y2" t="str">
-        <v>1240 W 6th St</v>
+        <v>220 Demo Street</v>
       </c>
       <c r="Z2" t="str">
         <v>Cleveland</v>
@@ -975,7 +975,7 @@
         <v>SSN</v>
       </c>
       <c r="BD2" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="BF2">
         <v>45392</v>
@@ -1065,7 +1065,7 @@
         <v>Carter</v>
       </c>
       <c r="CL2" t="str">
-        <v>OH1668243</v>
+        <v>OH0000075</v>
       </c>
       <c r="CM2" t="str">
         <v>OH</v>
@@ -1083,7 +1083,7 @@
         <v>46094</v>
       </c>
       <c r="CR2" t="str">
-        <v>(614) 821-5212</v>
+        <v>(614) 555-0107</v>
       </c>
       <c r="CS2" t="str">
         <v>Dr. Patricia Owens</v>
@@ -1199,22 +1199,22 @@
         <v>John Carter</v>
       </c>
       <c r="C3" t="str">
-        <v>1240 W 6th St, Cleveland, OH 44113</v>
+        <v>220 Demo Street, Cleveland, OH 44113</v>
       </c>
       <c r="D3" t="str">
-        <v>206-667-3424</v>
+        <v>206-555-0102</v>
       </c>
       <c r="E3" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="F3" t="str">
         <v>Huntington</v>
       </c>
       <c r="G3">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H3">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I3" t="str">
         <v>Medical Certification</v>
@@ -1223,7 +1223,7 @@
         <v>VALID</v>
       </c>
       <c r="K3" t="str">
-        <v>OH2933152</v>
+        <v>OH0000092</v>
       </c>
       <c r="L3">
         <v>46621</v>
@@ -1250,7 +1250,7 @@
         <v>M</v>
       </c>
       <c r="U3">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V3" t="str">
         <v>DRV-001.png</v>
@@ -1259,10 +1259,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X3" t="str">
-        <v>jcarter@yahoo.com</v>
+        <v>jcarter@example.com</v>
       </c>
       <c r="Y3" t="str">
-        <v>1240 W 6th St</v>
+        <v>220 Demo Street</v>
       </c>
       <c r="Z3" t="str">
         <v>Cleveland</v>
@@ -1337,7 +1337,7 @@
         <v>SSN</v>
       </c>
       <c r="BD3" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="BF3">
         <v>45392</v>
@@ -1427,7 +1427,7 @@
         <v>Carter</v>
       </c>
       <c r="CL3" t="str">
-        <v>OH1668244</v>
+        <v>OH0000076</v>
       </c>
       <c r="CM3" t="str">
         <v>OH</v>
@@ -1445,7 +1445,7 @@
         <v>46094</v>
       </c>
       <c r="CR3" t="str">
-        <v>(614) 821-5212</v>
+        <v>(614) 555-0107</v>
       </c>
       <c r="CS3" t="str">
         <v>Dr. Patricia Owens</v>
@@ -1561,22 +1561,22 @@
         <v>John Carter</v>
       </c>
       <c r="C4" t="str">
-        <v>1240 W 6th St, Cleveland, OH 44113</v>
+        <v>220 Demo Street, Cleveland, OH 44113</v>
       </c>
       <c r="D4" t="str">
-        <v>206-667-3424</v>
+        <v>206-555-0102</v>
       </c>
       <c r="E4" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="F4" t="str">
         <v>Huntington</v>
       </c>
       <c r="G4">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H4">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I4" t="str">
         <v>MVR Background Report</v>
@@ -1585,7 +1585,7 @@
         <v>VALID</v>
       </c>
       <c r="K4" t="str">
-        <v>OH6381314</v>
+        <v>OH0000111</v>
       </c>
       <c r="L4">
         <v>46621</v>
@@ -1612,7 +1612,7 @@
         <v>M</v>
       </c>
       <c r="U4">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V4" t="str">
         <v>DRV-001.png</v>
@@ -1621,10 +1621,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X4" t="str">
-        <v>jcarter@yahoo.com</v>
+        <v>jcarter@example.com</v>
       </c>
       <c r="Y4" t="str">
-        <v>1240 W 6th St</v>
+        <v>220 Demo Street</v>
       </c>
       <c r="Z4" t="str">
         <v>Cleveland</v>
@@ -1699,7 +1699,7 @@
         <v>SSN</v>
       </c>
       <c r="BD4" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="BF4">
         <v>45392</v>
@@ -1789,7 +1789,7 @@
         <v>Carter</v>
       </c>
       <c r="CL4" t="str">
-        <v>OH1668245</v>
+        <v>OH0000077</v>
       </c>
       <c r="CM4" t="str">
         <v>OH</v>
@@ -1807,7 +1807,7 @@
         <v>46094</v>
       </c>
       <c r="CR4" t="str">
-        <v>(614) 821-5212</v>
+        <v>(614) 555-0107</v>
       </c>
       <c r="CS4" t="str">
         <v>Dr. Patricia Owens</v>
@@ -1923,22 +1923,22 @@
         <v>John Carter</v>
       </c>
       <c r="C5" t="str">
-        <v>1240 W 6th St, Cleveland, OH 44113</v>
+        <v>220 Demo Street, Cleveland, OH 44113</v>
       </c>
       <c r="D5" t="str">
-        <v>206-667-3424</v>
+        <v>206-555-0102</v>
       </c>
       <c r="E5" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="F5" t="str">
         <v>Huntington</v>
       </c>
       <c r="G5">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H5">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I5" t="str">
         <v>Driver Application</v>
@@ -1947,7 +1947,7 @@
         <v>VALID</v>
       </c>
       <c r="K5" t="str">
-        <v>OH8275310</v>
+        <v>OH0000127</v>
       </c>
       <c r="L5">
         <v>46621</v>
@@ -1974,7 +1974,7 @@
         <v>M</v>
       </c>
       <c r="U5">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V5" t="str">
         <v>DRV-001.png</v>
@@ -1983,10 +1983,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X5" t="str">
-        <v>jcarter@yahoo.com</v>
+        <v>jcarter@example.com</v>
       </c>
       <c r="Y5" t="str">
-        <v>1240 W 6th St</v>
+        <v>220 Demo Street</v>
       </c>
       <c r="Z5" t="str">
         <v>Cleveland</v>
@@ -2061,7 +2061,7 @@
         <v>SSN</v>
       </c>
       <c r="BD5" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="BF5">
         <v>45392</v>
@@ -2151,7 +2151,7 @@
         <v>Carter</v>
       </c>
       <c r="CL5" t="str">
-        <v>OH1668246</v>
+        <v>OH0000078</v>
       </c>
       <c r="CM5" t="str">
         <v>OH</v>
@@ -2169,7 +2169,7 @@
         <v>46094</v>
       </c>
       <c r="CR5" t="str">
-        <v>(614) 821-5212</v>
+        <v>(614) 555-0107</v>
       </c>
       <c r="CS5" t="str">
         <v>Dr. Patricia Owens</v>
@@ -2285,22 +2285,22 @@
         <v>John Carter</v>
       </c>
       <c r="C6" t="str">
-        <v>1240 W 6th St, Cleveland, OH 44113</v>
+        <v>220 Demo Street, Cleveland, OH 44113</v>
       </c>
       <c r="D6" t="str">
-        <v>206-667-3424</v>
+        <v>206-555-0102</v>
       </c>
       <c r="E6" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="F6" t="str">
         <v>Huntington</v>
       </c>
       <c r="G6">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H6">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I6" t="str">
         <v>Road Test Certificate</v>
@@ -2309,7 +2309,7 @@
         <v>VALID</v>
       </c>
       <c r="K6" t="str">
-        <v>OH8643525</v>
+        <v>OH0000137</v>
       </c>
       <c r="L6">
         <v>46621</v>
@@ -2336,7 +2336,7 @@
         <v>M</v>
       </c>
       <c r="U6">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V6" t="str">
         <v>DRV-001.png</v>
@@ -2345,10 +2345,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X6" t="str">
-        <v>jcarter@yahoo.com</v>
+        <v>jcarter@example.com</v>
       </c>
       <c r="Y6" t="str">
-        <v>1240 W 6th St</v>
+        <v>220 Demo Street</v>
       </c>
       <c r="Z6" t="str">
         <v>Cleveland</v>
@@ -2423,7 +2423,7 @@
         <v>SSN</v>
       </c>
       <c r="BD6" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="BF6">
         <v>45392</v>
@@ -2513,7 +2513,7 @@
         <v>Carter</v>
       </c>
       <c r="CL6" t="str">
-        <v>OH1668247</v>
+        <v>OH0000079</v>
       </c>
       <c r="CM6" t="str">
         <v>OH</v>
@@ -2531,7 +2531,7 @@
         <v>46094</v>
       </c>
       <c r="CR6" t="str">
-        <v>(614) 821-5212</v>
+        <v>(614) 555-0107</v>
       </c>
       <c r="CS6" t="str">
         <v>Dr. Patricia Owens</v>
@@ -2647,22 +2647,22 @@
         <v>John Carter</v>
       </c>
       <c r="C7" t="str">
-        <v>1240 W 6th St, Cleveland, OH 44113</v>
+        <v>220 Demo Street, Cleveland, OH 44113</v>
       </c>
       <c r="D7" t="str">
-        <v>206-667-3424</v>
+        <v>206-555-0102</v>
       </c>
       <c r="E7" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="F7" t="str">
         <v>Huntington</v>
       </c>
       <c r="G7">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H7">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I7" t="str">
         <v>Incident/Accident Report</v>
@@ -2671,7 +2671,7 @@
         <v>VALID</v>
       </c>
       <c r="K7" t="str">
-        <v>OH8694835</v>
+        <v>OH0000138</v>
       </c>
       <c r="L7">
         <v>46621</v>
@@ -2701,7 +2701,7 @@
         <v>M</v>
       </c>
       <c r="U7">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V7" t="str">
         <v>DRV-001.png</v>
@@ -2710,10 +2710,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X7" t="str">
-        <v>jcarter@yahoo.com</v>
+        <v>jcarter@example.com</v>
       </c>
       <c r="Y7" t="str">
-        <v>1240 W 6th St</v>
+        <v>220 Demo Street</v>
       </c>
       <c r="Z7" t="str">
         <v>Cleveland</v>
@@ -2788,7 +2788,7 @@
         <v>SSN</v>
       </c>
       <c r="BD7" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="BF7">
         <v>45392</v>
@@ -2878,7 +2878,7 @@
         <v>Carter</v>
       </c>
       <c r="CL7" t="str">
-        <v>OH1668248</v>
+        <v>OH0000080</v>
       </c>
       <c r="CM7" t="str">
         <v>OH</v>
@@ -2896,7 +2896,7 @@
         <v>46094</v>
       </c>
       <c r="CR7" t="str">
-        <v>(614) 821-5212</v>
+        <v>(614) 555-0107</v>
       </c>
       <c r="CS7" t="str">
         <v>Dr. Patricia Owens</v>
@@ -3012,22 +3012,22 @@
         <v>John Carter</v>
       </c>
       <c r="C8" t="str">
-        <v>1240 W 6th St, Cleveland, OH 44113</v>
+        <v>220 Demo Street, Cleveland, OH 44113</v>
       </c>
       <c r="D8" t="str">
-        <v>206-667-3424</v>
+        <v>206-555-0102</v>
       </c>
       <c r="E8" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="F8" t="str">
         <v>Huntington</v>
       </c>
       <c r="G8">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H8">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I8" t="str">
         <v>Direct Deposit Form</v>
@@ -3036,7 +3036,7 @@
         <v>VALID</v>
       </c>
       <c r="K8" t="str">
-        <v>OH7359899</v>
+        <v>OH0000124</v>
       </c>
       <c r="L8">
         <v>46621</v>
@@ -3063,7 +3063,7 @@
         <v>M</v>
       </c>
       <c r="U8">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V8" t="str">
         <v>DRV-001.png</v>
@@ -3072,10 +3072,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X8" t="str">
-        <v>jcarter@yahoo.com</v>
+        <v>jcarter@example.com</v>
       </c>
       <c r="Y8" t="str">
-        <v>1240 W 6th St</v>
+        <v>220 Demo Street</v>
       </c>
       <c r="Z8" t="str">
         <v>Cleveland</v>
@@ -3150,7 +3150,7 @@
         <v>SSN</v>
       </c>
       <c r="BD8" t="str">
-        <v>***-**-9443</v>
+        <v>***-**-0123</v>
       </c>
       <c r="BF8">
         <v>45392</v>
@@ -3240,7 +3240,7 @@
         <v>Carter</v>
       </c>
       <c r="CL8" t="str">
-        <v>OH1668249</v>
+        <v>OH0000081</v>
       </c>
       <c r="CM8" t="str">
         <v>OH</v>
@@ -3258,7 +3258,7 @@
         <v>46094</v>
       </c>
       <c r="CR8" t="str">
-        <v>(614) 821-5212</v>
+        <v>(614) 555-0107</v>
       </c>
       <c r="CS8" t="str">
         <v>Dr. Patricia Owens</v>
@@ -3374,22 +3374,22 @@
         <v>Maria Lopez</v>
       </c>
       <c r="C9" t="str">
-        <v>450 N Michigan Ave, Chicago, IL 60611</v>
+        <v>770 Demo Street, Chicago, IL 60611</v>
       </c>
       <c r="D9" t="str">
-        <v>707-773-6386</v>
+        <v>707-555-0100</v>
       </c>
       <c r="E9" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="F9" t="str">
         <v>Chase</v>
       </c>
       <c r="G9">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H9">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I9" t="str">
         <v>CDL Summary</v>
@@ -3398,7 +3398,7 @@
         <v>VALID</v>
       </c>
       <c r="K9" t="str">
-        <v>IL3091126</v>
+        <v>IL0000041</v>
       </c>
       <c r="L9">
         <v>46518</v>
@@ -3425,7 +3425,7 @@
         <v>F</v>
       </c>
       <c r="U9">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V9" t="str">
         <v>DRV-002.png</v>
@@ -3434,10 +3434,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X9" t="str">
-        <v>marialopez@aol.com</v>
+        <v>marialopez@example.com</v>
       </c>
       <c r="Y9" t="str">
-        <v>450 N Michigan Ave</v>
+        <v>770 Demo Street</v>
       </c>
       <c r="Z9" t="str">
         <v>Chicago</v>
@@ -3521,7 +3521,7 @@
         <v>SSN</v>
       </c>
       <c r="BD9" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="BF9">
         <v>45446</v>
@@ -3614,7 +3614,7 @@
         <v>Lopez</v>
       </c>
       <c r="CL9" t="str">
-        <v>IL3091126</v>
+        <v>IL0000041</v>
       </c>
       <c r="CM9" t="str">
         <v>IL</v>
@@ -3632,7 +3632,7 @@
         <v>46596</v>
       </c>
       <c r="CR9" t="str">
-        <v>(312) 284-7914</v>
+        <v>(312) 555-0101</v>
       </c>
       <c r="CS9" t="str">
         <v>Dr. Kevin Marshall</v>
@@ -3748,22 +3748,22 @@
         <v>Maria Lopez</v>
       </c>
       <c r="C10" t="str">
-        <v>450 N Michigan Ave, Chicago, IL 60611</v>
+        <v>770 Demo Street, Chicago, IL 60611</v>
       </c>
       <c r="D10" t="str">
-        <v>707-773-6386</v>
+        <v>707-555-0100</v>
       </c>
       <c r="E10" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="F10" t="str">
         <v>Chase</v>
       </c>
       <c r="G10">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H10">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I10" t="str">
         <v>Medical Certification</v>
@@ -3772,7 +3772,7 @@
         <v>VALID</v>
       </c>
       <c r="K10" t="str">
-        <v>IL9530000</v>
+        <v>IL0000068</v>
       </c>
       <c r="L10">
         <v>46518</v>
@@ -3799,7 +3799,7 @@
         <v>F</v>
       </c>
       <c r="U10">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V10" t="str">
         <v>DRV-002.png</v>
@@ -3808,10 +3808,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X10" t="str">
-        <v>marialopez@aol.com</v>
+        <v>marialopez@example.com</v>
       </c>
       <c r="Y10" t="str">
-        <v>450 N Michigan Ave</v>
+        <v>770 Demo Street</v>
       </c>
       <c r="Z10" t="str">
         <v>Chicago</v>
@@ -3895,7 +3895,7 @@
         <v>SSN</v>
       </c>
       <c r="BD10" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="BF10">
         <v>45446</v>
@@ -3988,7 +3988,7 @@
         <v>Lopez</v>
       </c>
       <c r="CL10" t="str">
-        <v>IL3091127</v>
+        <v>IL0000042</v>
       </c>
       <c r="CM10" t="str">
         <v>IL</v>
@@ -4006,7 +4006,7 @@
         <v>46596</v>
       </c>
       <c r="CR10" t="str">
-        <v>(312) 284-7914</v>
+        <v>(312) 555-0101</v>
       </c>
       <c r="CS10" t="str">
         <v>Dr. Kevin Marshall</v>
@@ -4122,22 +4122,22 @@
         <v>Maria Lopez</v>
       </c>
       <c r="C11" t="str">
-        <v>450 N Michigan Ave, Chicago, IL 60611</v>
+        <v>770 Demo Street, Chicago, IL 60611</v>
       </c>
       <c r="D11" t="str">
-        <v>707-773-6386</v>
+        <v>707-555-0100</v>
       </c>
       <c r="E11" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="F11" t="str">
         <v>Chase</v>
       </c>
       <c r="G11">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H11">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I11" t="str">
         <v>MVR Background Report</v>
@@ -4146,7 +4146,7 @@
         <v>VALID</v>
       </c>
       <c r="K11" t="str">
-        <v>IL3900948</v>
+        <v>IL0000056</v>
       </c>
       <c r="L11">
         <v>46518</v>
@@ -4173,7 +4173,7 @@
         <v>F</v>
       </c>
       <c r="U11">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V11" t="str">
         <v>DRV-002.png</v>
@@ -4182,10 +4182,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X11" t="str">
-        <v>marialopez@aol.com</v>
+        <v>marialopez@example.com</v>
       </c>
       <c r="Y11" t="str">
-        <v>450 N Michigan Ave</v>
+        <v>770 Demo Street</v>
       </c>
       <c r="Z11" t="str">
         <v>Chicago</v>
@@ -4269,7 +4269,7 @@
         <v>SSN</v>
       </c>
       <c r="BD11" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="BF11">
         <v>45446</v>
@@ -4362,7 +4362,7 @@
         <v>Lopez</v>
       </c>
       <c r="CL11" t="str">
-        <v>IL3091128</v>
+        <v>IL0000043</v>
       </c>
       <c r="CM11" t="str">
         <v>IL</v>
@@ -4380,7 +4380,7 @@
         <v>46596</v>
       </c>
       <c r="CR11" t="str">
-        <v>(312) 284-7914</v>
+        <v>(312) 555-0101</v>
       </c>
       <c r="CS11" t="str">
         <v>Dr. Kevin Marshall</v>
@@ -4496,22 +4496,22 @@
         <v>Maria Lopez</v>
       </c>
       <c r="C12" t="str">
-        <v>450 N Michigan Ave, Chicago, IL 60611</v>
+        <v>770 Demo Street, Chicago, IL 60611</v>
       </c>
       <c r="D12" t="str">
-        <v>707-773-6386</v>
+        <v>707-555-0100</v>
       </c>
       <c r="E12" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="F12" t="str">
         <v>Chase</v>
       </c>
       <c r="G12">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H12">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I12" t="str">
         <v>Driver Application</v>
@@ -4520,7 +4520,7 @@
         <v>VALID</v>
       </c>
       <c r="K12" t="str">
-        <v>IL6663817</v>
+        <v>IL0000065</v>
       </c>
       <c r="L12">
         <v>46518</v>
@@ -4547,7 +4547,7 @@
         <v>F</v>
       </c>
       <c r="U12">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V12" t="str">
         <v>DRV-002.png</v>
@@ -4556,10 +4556,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X12" t="str">
-        <v>marialopez@aol.com</v>
+        <v>marialopez@example.com</v>
       </c>
       <c r="Y12" t="str">
-        <v>450 N Michigan Ave</v>
+        <v>770 Demo Street</v>
       </c>
       <c r="Z12" t="str">
         <v>Chicago</v>
@@ -4643,7 +4643,7 @@
         <v>SSN</v>
       </c>
       <c r="BD12" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="BF12">
         <v>45446</v>
@@ -4736,7 +4736,7 @@
         <v>Lopez</v>
       </c>
       <c r="CL12" t="str">
-        <v>IL3091129</v>
+        <v>IL0000044</v>
       </c>
       <c r="CM12" t="str">
         <v>IL</v>
@@ -4754,7 +4754,7 @@
         <v>46596</v>
       </c>
       <c r="CR12" t="str">
-        <v>(312) 284-7914</v>
+        <v>(312) 555-0101</v>
       </c>
       <c r="CS12" t="str">
         <v>Dr. Kevin Marshall</v>
@@ -4870,22 +4870,22 @@
         <v>Maria Lopez</v>
       </c>
       <c r="C13" t="str">
-        <v>450 N Michigan Ave, Chicago, IL 60611</v>
+        <v>770 Demo Street, Chicago, IL 60611</v>
       </c>
       <c r="D13" t="str">
-        <v>707-773-6386</v>
+        <v>707-555-0100</v>
       </c>
       <c r="E13" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="F13" t="str">
         <v>Chase</v>
       </c>
       <c r="G13">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H13">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I13" t="str">
         <v>Road Test Certificate</v>
@@ -4894,7 +4894,7 @@
         <v>VALID</v>
       </c>
       <c r="K13" t="str">
-        <v>IL9293900</v>
+        <v>IL0000067</v>
       </c>
       <c r="L13">
         <v>46518</v>
@@ -4921,7 +4921,7 @@
         <v>F</v>
       </c>
       <c r="U13">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V13" t="str">
         <v>DRV-002.png</v>
@@ -4930,10 +4930,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X13" t="str">
-        <v>marialopez@aol.com</v>
+        <v>marialopez@example.com</v>
       </c>
       <c r="Y13" t="str">
-        <v>450 N Michigan Ave</v>
+        <v>770 Demo Street</v>
       </c>
       <c r="Z13" t="str">
         <v>Chicago</v>
@@ -5017,7 +5017,7 @@
         <v>SSN</v>
       </c>
       <c r="BD13" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="BF13">
         <v>45446</v>
@@ -5110,7 +5110,7 @@
         <v>Lopez</v>
       </c>
       <c r="CL13" t="str">
-        <v>IL3091130</v>
+        <v>IL0000045</v>
       </c>
       <c r="CM13" t="str">
         <v>IL</v>
@@ -5128,7 +5128,7 @@
         <v>46596</v>
       </c>
       <c r="CR13" t="str">
-        <v>(312) 284-7914</v>
+        <v>(312) 555-0101</v>
       </c>
       <c r="CS13" t="str">
         <v>Dr. Kevin Marshall</v>
@@ -5244,22 +5244,22 @@
         <v>Maria Lopez</v>
       </c>
       <c r="C14" t="str">
-        <v>450 N Michigan Ave, Chicago, IL 60611</v>
+        <v>770 Demo Street, Chicago, IL 60611</v>
       </c>
       <c r="D14" t="str">
-        <v>707-773-6386</v>
+        <v>707-555-0100</v>
       </c>
       <c r="E14" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="F14" t="str">
         <v>Chase</v>
       </c>
       <c r="G14">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H14">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I14" t="str">
         <v>Incident/Accident Report</v>
@@ -5268,7 +5268,7 @@
         <v>VALID</v>
       </c>
       <c r="K14" t="str">
-        <v>IL4346440</v>
+        <v>IL0000058</v>
       </c>
       <c r="L14">
         <v>46518</v>
@@ -5298,7 +5298,7 @@
         <v>F</v>
       </c>
       <c r="U14">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V14" t="str">
         <v>DRV-002.png</v>
@@ -5307,10 +5307,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X14" t="str">
-        <v>marialopez@aol.com</v>
+        <v>marialopez@example.com</v>
       </c>
       <c r="Y14" t="str">
-        <v>450 N Michigan Ave</v>
+        <v>770 Demo Street</v>
       </c>
       <c r="Z14" t="str">
         <v>Chicago</v>
@@ -5394,7 +5394,7 @@
         <v>SSN</v>
       </c>
       <c r="BD14" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="BF14">
         <v>45446</v>
@@ -5487,7 +5487,7 @@
         <v>Lopez</v>
       </c>
       <c r="CL14" t="str">
-        <v>IL3091131</v>
+        <v>IL0000046</v>
       </c>
       <c r="CM14" t="str">
         <v>IL</v>
@@ -5505,7 +5505,7 @@
         <v>46596</v>
       </c>
       <c r="CR14" t="str">
-        <v>(312) 284-7914</v>
+        <v>(312) 555-0101</v>
       </c>
       <c r="CS14" t="str">
         <v>Dr. Kevin Marshall</v>
@@ -5621,22 +5621,22 @@
         <v>Maria Lopez</v>
       </c>
       <c r="C15" t="str">
-        <v>450 N Michigan Ave, Chicago, IL 60611</v>
+        <v>770 Demo Street, Chicago, IL 60611</v>
       </c>
       <c r="D15" t="str">
-        <v>707-773-6386</v>
+        <v>707-555-0100</v>
       </c>
       <c r="E15" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="F15" t="str">
         <v>Chase</v>
       </c>
       <c r="G15">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H15">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I15" t="str">
         <v>Direct Deposit Form</v>
@@ -5645,7 +5645,7 @@
         <v>VALID</v>
       </c>
       <c r="K15" t="str">
-        <v>IL4913140</v>
+        <v>IL0000061</v>
       </c>
       <c r="L15">
         <v>46518</v>
@@ -5672,7 +5672,7 @@
         <v>F</v>
       </c>
       <c r="U15">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V15" t="str">
         <v>DRV-002.png</v>
@@ -5681,10 +5681,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X15" t="str">
-        <v>marialopez@aol.com</v>
+        <v>marialopez@example.com</v>
       </c>
       <c r="Y15" t="str">
-        <v>450 N Michigan Ave</v>
+        <v>770 Demo Street</v>
       </c>
       <c r="Z15" t="str">
         <v>Chicago</v>
@@ -5768,7 +5768,7 @@
         <v>SSN</v>
       </c>
       <c r="BD15" t="str">
-        <v>***-**-3407</v>
+        <v>***-**-0105</v>
       </c>
       <c r="BF15">
         <v>45446</v>
@@ -5861,7 +5861,7 @@
         <v>Lopez</v>
       </c>
       <c r="CL15" t="str">
-        <v>IL3091132</v>
+        <v>IL0000047</v>
       </c>
       <c r="CM15" t="str">
         <v>IL</v>
@@ -5879,7 +5879,7 @@
         <v>46596</v>
       </c>
       <c r="CR15" t="str">
-        <v>(312) 284-7914</v>
+        <v>(312) 555-0101</v>
       </c>
       <c r="CS15" t="str">
         <v>Dr. Kevin Marshall</v>
@@ -5995,22 +5995,22 @@
         <v>Alex Kim</v>
       </c>
       <c r="C16" t="str">
-        <v>780 Peachtree St, Atlanta, GA 30308</v>
+        <v>960 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D16" t="str">
-        <v>675-486-1335</v>
+        <v>675-555-0100</v>
       </c>
       <c r="E16" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="F16" t="str">
         <v>Chase</v>
       </c>
       <c r="G16">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H16">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I16" t="str">
         <v>CDL Summary</v>
@@ -6019,7 +6019,7 @@
         <v>VALID</v>
       </c>
       <c r="K16" t="str">
-        <v>GA7446431</v>
+        <v>GA0000013</v>
       </c>
       <c r="L16">
         <v>46420</v>
@@ -6046,7 +6046,7 @@
         <v>M</v>
       </c>
       <c r="U16">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V16" t="str">
         <v>DRV-003.png</v>
@@ -6055,10 +6055,10 @@
         <v>Asian</v>
       </c>
       <c r="X16" t="str">
-        <v>alexkim@gmail.com</v>
+        <v>alexkim@example.com</v>
       </c>
       <c r="Y16" t="str">
-        <v>780 Peachtree St</v>
+        <v>960 Demo Street</v>
       </c>
       <c r="Z16" t="str">
         <v>Atlanta</v>
@@ -6133,7 +6133,7 @@
         <v>SSN</v>
       </c>
       <c r="BD16" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="BF16">
         <v>45488</v>
@@ -6226,7 +6226,7 @@
         <v>Kim</v>
       </c>
       <c r="CL16" t="str">
-        <v>GA7446431</v>
+        <v>GA0000013</v>
       </c>
       <c r="CM16" t="str">
         <v>GA</v>
@@ -6244,7 +6244,7 @@
         <v>46659</v>
       </c>
       <c r="CR16" t="str">
-        <v>(404) 720-5860</v>
+        <v>(404) 555-0107</v>
       </c>
       <c r="CS16" t="str">
         <v>Dr. Lisa Bennett</v>
@@ -6360,22 +6360,22 @@
         <v>Alex Kim</v>
       </c>
       <c r="C17" t="str">
-        <v>780 Peachtree St, Atlanta, GA 30308</v>
+        <v>960 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D17" t="str">
-        <v>675-486-1335</v>
+        <v>675-555-0100</v>
       </c>
       <c r="E17" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="F17" t="str">
         <v>Chase</v>
       </c>
       <c r="G17">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H17">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I17" t="str">
         <v>Medical Certification</v>
@@ -6384,7 +6384,7 @@
         <v>VALID</v>
       </c>
       <c r="K17" t="str">
-        <v>GA3549920</v>
+        <v>GA0000006</v>
       </c>
       <c r="L17">
         <v>46420</v>
@@ -6411,7 +6411,7 @@
         <v>M</v>
       </c>
       <c r="U17">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V17" t="str">
         <v>DRV-003.png</v>
@@ -6420,10 +6420,10 @@
         <v>Asian</v>
       </c>
       <c r="X17" t="str">
-        <v>alexkim@gmail.com</v>
+        <v>alexkim@example.com</v>
       </c>
       <c r="Y17" t="str">
-        <v>780 Peachtree St</v>
+        <v>960 Demo Street</v>
       </c>
       <c r="Z17" t="str">
         <v>Atlanta</v>
@@ -6498,7 +6498,7 @@
         <v>SSN</v>
       </c>
       <c r="BD17" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="BF17">
         <v>45488</v>
@@ -6591,7 +6591,7 @@
         <v>Kim</v>
       </c>
       <c r="CL17" t="str">
-        <v>GA7446432</v>
+        <v>GA0000014</v>
       </c>
       <c r="CM17" t="str">
         <v>GA</v>
@@ -6609,7 +6609,7 @@
         <v>46659</v>
       </c>
       <c r="CR17" t="str">
-        <v>(404) 720-5860</v>
+        <v>(404) 555-0107</v>
       </c>
       <c r="CS17" t="str">
         <v>Dr. Lisa Bennett</v>
@@ -6725,22 +6725,22 @@
         <v>Alex Kim</v>
       </c>
       <c r="C18" t="str">
-        <v>780 Peachtree St, Atlanta, GA 30308</v>
+        <v>960 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D18" t="str">
-        <v>675-486-1335</v>
+        <v>675-555-0100</v>
       </c>
       <c r="E18" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="F18" t="str">
         <v>Chase</v>
       </c>
       <c r="G18">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H18">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I18" t="str">
         <v>MVR Background Report</v>
@@ -6749,7 +6749,7 @@
         <v>VALID</v>
       </c>
       <c r="K18" t="str">
-        <v>GA5957495</v>
+        <v>GA0000011</v>
       </c>
       <c r="L18">
         <v>46420</v>
@@ -6776,7 +6776,7 @@
         <v>M</v>
       </c>
       <c r="U18">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V18" t="str">
         <v>DRV-003.png</v>
@@ -6785,10 +6785,10 @@
         <v>Asian</v>
       </c>
       <c r="X18" t="str">
-        <v>alexkim@gmail.com</v>
+        <v>alexkim@example.com</v>
       </c>
       <c r="Y18" t="str">
-        <v>780 Peachtree St</v>
+        <v>960 Demo Street</v>
       </c>
       <c r="Z18" t="str">
         <v>Atlanta</v>
@@ -6863,7 +6863,7 @@
         <v>SSN</v>
       </c>
       <c r="BD18" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="BF18">
         <v>45488</v>
@@ -6956,7 +6956,7 @@
         <v>Kim</v>
       </c>
       <c r="CL18" t="str">
-        <v>GA7446433</v>
+        <v>GA0000015</v>
       </c>
       <c r="CM18" t="str">
         <v>GA</v>
@@ -6974,7 +6974,7 @@
         <v>46659</v>
       </c>
       <c r="CR18" t="str">
-        <v>(404) 720-5860</v>
+        <v>(404) 555-0107</v>
       </c>
       <c r="CS18" t="str">
         <v>Dr. Lisa Bennett</v>
@@ -7090,22 +7090,22 @@
         <v>Alex Kim</v>
       </c>
       <c r="C19" t="str">
-        <v>780 Peachtree St, Atlanta, GA 30308</v>
+        <v>960 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D19" t="str">
-        <v>675-486-1335</v>
+        <v>675-555-0100</v>
       </c>
       <c r="E19" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="F19" t="str">
         <v>Chase</v>
       </c>
       <c r="G19">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H19">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I19" t="str">
         <v>Driver Application</v>
@@ -7114,7 +7114,7 @@
         <v>VALID</v>
       </c>
       <c r="K19" t="str">
-        <v>GA3499514</v>
+        <v>GA0000005</v>
       </c>
       <c r="L19">
         <v>46420</v>
@@ -7141,7 +7141,7 @@
         <v>M</v>
       </c>
       <c r="U19">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V19" t="str">
         <v>DRV-003.png</v>
@@ -7150,10 +7150,10 @@
         <v>Asian</v>
       </c>
       <c r="X19" t="str">
-        <v>alexkim@gmail.com</v>
+        <v>alexkim@example.com</v>
       </c>
       <c r="Y19" t="str">
-        <v>780 Peachtree St</v>
+        <v>960 Demo Street</v>
       </c>
       <c r="Z19" t="str">
         <v>Atlanta</v>
@@ -7228,7 +7228,7 @@
         <v>SSN</v>
       </c>
       <c r="BD19" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="BF19">
         <v>45488</v>
@@ -7321,7 +7321,7 @@
         <v>Kim</v>
       </c>
       <c r="CL19" t="str">
-        <v>GA7446434</v>
+        <v>GA0000016</v>
       </c>
       <c r="CM19" t="str">
         <v>GA</v>
@@ -7339,7 +7339,7 @@
         <v>46659</v>
       </c>
       <c r="CR19" t="str">
-        <v>(404) 720-5860</v>
+        <v>(404) 555-0107</v>
       </c>
       <c r="CS19" t="str">
         <v>Dr. Lisa Bennett</v>
@@ -7455,22 +7455,22 @@
         <v>Alex Kim</v>
       </c>
       <c r="C20" t="str">
-        <v>780 Peachtree St, Atlanta, GA 30308</v>
+        <v>960 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D20" t="str">
-        <v>675-486-1335</v>
+        <v>675-555-0100</v>
       </c>
       <c r="E20" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="F20" t="str">
         <v>Chase</v>
       </c>
       <c r="G20">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H20">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I20" t="str">
         <v>Road Test Certificate</v>
@@ -7479,7 +7479,7 @@
         <v>VALID</v>
       </c>
       <c r="K20" t="str">
-        <v>GA3381500</v>
+        <v>GA0000004</v>
       </c>
       <c r="L20">
         <v>46420</v>
@@ -7506,7 +7506,7 @@
         <v>M</v>
       </c>
       <c r="U20">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V20" t="str">
         <v>DRV-003.png</v>
@@ -7515,10 +7515,10 @@
         <v>Asian</v>
       </c>
       <c r="X20" t="str">
-        <v>alexkim@gmail.com</v>
+        <v>alexkim@example.com</v>
       </c>
       <c r="Y20" t="str">
-        <v>780 Peachtree St</v>
+        <v>960 Demo Street</v>
       </c>
       <c r="Z20" t="str">
         <v>Atlanta</v>
@@ -7593,7 +7593,7 @@
         <v>SSN</v>
       </c>
       <c r="BD20" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="BF20">
         <v>45488</v>
@@ -7686,7 +7686,7 @@
         <v>Kim</v>
       </c>
       <c r="CL20" t="str">
-        <v>GA7446435</v>
+        <v>GA0000017</v>
       </c>
       <c r="CM20" t="str">
         <v>GA</v>
@@ -7704,7 +7704,7 @@
         <v>46659</v>
       </c>
       <c r="CR20" t="str">
-        <v>(404) 720-5860</v>
+        <v>(404) 555-0107</v>
       </c>
       <c r="CS20" t="str">
         <v>Dr. Lisa Bennett</v>
@@ -7820,22 +7820,22 @@
         <v>Alex Kim</v>
       </c>
       <c r="C21" t="str">
-        <v>780 Peachtree St, Atlanta, GA 30308</v>
+        <v>960 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D21" t="str">
-        <v>675-486-1335</v>
+        <v>675-555-0100</v>
       </c>
       <c r="E21" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="F21" t="str">
         <v>Chase</v>
       </c>
       <c r="G21">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H21">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I21" t="str">
         <v>Incident/Accident Report</v>
@@ -7844,7 +7844,7 @@
         <v>VALID</v>
       </c>
       <c r="K21" t="str">
-        <v>GA8768417</v>
+        <v>GA0000027</v>
       </c>
       <c r="L21">
         <v>46420</v>
@@ -7874,7 +7874,7 @@
         <v>M</v>
       </c>
       <c r="U21">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V21" t="str">
         <v>DRV-003.png</v>
@@ -7883,10 +7883,10 @@
         <v>Asian</v>
       </c>
       <c r="X21" t="str">
-        <v>alexkim@gmail.com</v>
+        <v>alexkim@example.com</v>
       </c>
       <c r="Y21" t="str">
-        <v>780 Peachtree St</v>
+        <v>960 Demo Street</v>
       </c>
       <c r="Z21" t="str">
         <v>Atlanta</v>
@@ -7961,7 +7961,7 @@
         <v>SSN</v>
       </c>
       <c r="BD21" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="BF21">
         <v>45488</v>
@@ -8054,7 +8054,7 @@
         <v>Kim</v>
       </c>
       <c r="CL21" t="str">
-        <v>GA7446436</v>
+        <v>GA0000018</v>
       </c>
       <c r="CM21" t="str">
         <v>GA</v>
@@ -8072,7 +8072,7 @@
         <v>46659</v>
       </c>
       <c r="CR21" t="str">
-        <v>(404) 720-5860</v>
+        <v>(404) 555-0107</v>
       </c>
       <c r="CS21" t="str">
         <v>Dr. Lisa Bennett</v>
@@ -8188,22 +8188,22 @@
         <v>Alex Kim</v>
       </c>
       <c r="C22" t="str">
-        <v>780 Peachtree St, Atlanta, GA 30308</v>
+        <v>960 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D22" t="str">
-        <v>675-486-1335</v>
+        <v>675-555-0100</v>
       </c>
       <c r="E22" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="F22" t="str">
         <v>Chase</v>
       </c>
       <c r="G22">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H22">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I22" t="str">
         <v>Direct Deposit Form</v>
@@ -8212,7 +8212,7 @@
         <v>VALID</v>
       </c>
       <c r="K22" t="str">
-        <v>GA1828575</v>
+        <v>GA0000002</v>
       </c>
       <c r="L22">
         <v>46420</v>
@@ -8239,7 +8239,7 @@
         <v>M</v>
       </c>
       <c r="U22">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V22" t="str">
         <v>DRV-003.png</v>
@@ -8248,10 +8248,10 @@
         <v>Asian</v>
       </c>
       <c r="X22" t="str">
-        <v>alexkim@gmail.com</v>
+        <v>alexkim@example.com</v>
       </c>
       <c r="Y22" t="str">
-        <v>780 Peachtree St</v>
+        <v>960 Demo Street</v>
       </c>
       <c r="Z22" t="str">
         <v>Atlanta</v>
@@ -8326,7 +8326,7 @@
         <v>SSN</v>
       </c>
       <c r="BD22" t="str">
-        <v>***-**-7047</v>
+        <v>***-**-0116</v>
       </c>
       <c r="BF22">
         <v>45488</v>
@@ -8419,7 +8419,7 @@
         <v>Kim</v>
       </c>
       <c r="CL22" t="str">
-        <v>GA7446437</v>
+        <v>GA0000019</v>
       </c>
       <c r="CM22" t="str">
         <v>GA</v>
@@ -8437,7 +8437,7 @@
         <v>46659</v>
       </c>
       <c r="CR22" t="str">
-        <v>(404) 720-5860</v>
+        <v>(404) 555-0107</v>
       </c>
       <c r="CS22" t="str">
         <v>Dr. Lisa Bennett</v>
@@ -8553,22 +8553,22 @@
         <v>Priya Patel</v>
       </c>
       <c r="C23" t="str">
-        <v>2200 Superior Ave, Cleveland, OH 44114</v>
+        <v>520 Demo Street, Cleveland, OH 44114</v>
       </c>
       <c r="D23" t="str">
-        <v>359-469-5960</v>
+        <v>359-555-0100</v>
       </c>
       <c r="E23" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="F23" t="str">
         <v>Chase</v>
       </c>
       <c r="G23">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H23">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I23" t="str">
         <v>CDL Summary</v>
@@ -8577,7 +8577,7 @@
         <v>VALID</v>
       </c>
       <c r="K23" t="str">
-        <v>OH8493496</v>
+        <v>OH0000130</v>
       </c>
       <c r="L23">
         <v>46739</v>
@@ -8604,7 +8604,7 @@
         <v>F</v>
       </c>
       <c r="U23">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V23" t="str">
         <v>DRV-004.png</v>
@@ -8613,10 +8613,10 @@
         <v>South Asian</v>
       </c>
       <c r="X23" t="str">
-        <v>priyapatel@yahoo.com</v>
+        <v>priyapatel@example.com</v>
       </c>
       <c r="Y23" t="str">
-        <v>2200 Superior Ave</v>
+        <v>520 Demo Street</v>
       </c>
       <c r="Z23" t="str">
         <v>Cleveland</v>
@@ -8697,7 +8697,7 @@
         <v>SSN</v>
       </c>
       <c r="BD23" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="BF23">
         <v>45432</v>
@@ -8790,7 +8790,7 @@
         <v>Patel</v>
       </c>
       <c r="CL23" t="str">
-        <v>OH8493496</v>
+        <v>OH0000130</v>
       </c>
       <c r="CM23" t="str">
         <v>OH</v>
@@ -8808,7 +8808,7 @@
         <v>46486</v>
       </c>
       <c r="CR23" t="str">
-        <v>(614) 897-8705</v>
+        <v>(614) 555-0111</v>
       </c>
       <c r="CS23" t="str">
         <v>Dr. Ramon Ortiz</v>
@@ -8924,22 +8924,22 @@
         <v>Priya Patel</v>
       </c>
       <c r="C24" t="str">
-        <v>2200 Superior Ave, Cleveland, OH 44114</v>
+        <v>520 Demo Street, Cleveland, OH 44114</v>
       </c>
       <c r="D24" t="str">
-        <v>359-469-5960</v>
+        <v>359-555-0100</v>
       </c>
       <c r="E24" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="F24" t="str">
         <v>Chase</v>
       </c>
       <c r="G24">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H24">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I24" t="str">
         <v>Medical Certification</v>
@@ -8948,7 +8948,7 @@
         <v>VALID</v>
       </c>
       <c r="K24" t="str">
-        <v>OH4694295</v>
+        <v>OH0000099</v>
       </c>
       <c r="L24">
         <v>46739</v>
@@ -8975,7 +8975,7 @@
         <v>F</v>
       </c>
       <c r="U24">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V24" t="str">
         <v>DRV-004.png</v>
@@ -8984,10 +8984,10 @@
         <v>South Asian</v>
       </c>
       <c r="X24" t="str">
-        <v>priyapatel@yahoo.com</v>
+        <v>priyapatel@example.com</v>
       </c>
       <c r="Y24" t="str">
-        <v>2200 Superior Ave</v>
+        <v>520 Demo Street</v>
       </c>
       <c r="Z24" t="str">
         <v>Cleveland</v>
@@ -9068,7 +9068,7 @@
         <v>SSN</v>
       </c>
       <c r="BD24" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="BF24">
         <v>45432</v>
@@ -9161,7 +9161,7 @@
         <v>Patel</v>
       </c>
       <c r="CL24" t="str">
-        <v>OH8493497</v>
+        <v>OH0000131</v>
       </c>
       <c r="CM24" t="str">
         <v>OH</v>
@@ -9179,7 +9179,7 @@
         <v>46486</v>
       </c>
       <c r="CR24" t="str">
-        <v>(614) 897-8705</v>
+        <v>(614) 555-0111</v>
       </c>
       <c r="CS24" t="str">
         <v>Dr. Ramon Ortiz</v>
@@ -9295,22 +9295,22 @@
         <v>Priya Patel</v>
       </c>
       <c r="C25" t="str">
-        <v>2200 Superior Ave, Cleveland, OH 44114</v>
+        <v>520 Demo Street, Cleveland, OH 44114</v>
       </c>
       <c r="D25" t="str">
-        <v>359-469-5960</v>
+        <v>359-555-0100</v>
       </c>
       <c r="E25" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="F25" t="str">
         <v>Chase</v>
       </c>
       <c r="G25">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H25">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I25" t="str">
         <v>MVR Background Report</v>
@@ -9319,7 +9319,7 @@
         <v>VALID</v>
       </c>
       <c r="K25" t="str">
-        <v>OH7280038</v>
+        <v>OH0000123</v>
       </c>
       <c r="L25">
         <v>46739</v>
@@ -9346,7 +9346,7 @@
         <v>F</v>
       </c>
       <c r="U25">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V25" t="str">
         <v>DRV-004.png</v>
@@ -9355,10 +9355,10 @@
         <v>South Asian</v>
       </c>
       <c r="X25" t="str">
-        <v>priyapatel@yahoo.com</v>
+        <v>priyapatel@example.com</v>
       </c>
       <c r="Y25" t="str">
-        <v>2200 Superior Ave</v>
+        <v>520 Demo Street</v>
       </c>
       <c r="Z25" t="str">
         <v>Cleveland</v>
@@ -9439,7 +9439,7 @@
         <v>SSN</v>
       </c>
       <c r="BD25" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="BF25">
         <v>45432</v>
@@ -9532,7 +9532,7 @@
         <v>Patel</v>
       </c>
       <c r="CL25" t="str">
-        <v>OH8493498</v>
+        <v>OH0000132</v>
       </c>
       <c r="CM25" t="str">
         <v>OH</v>
@@ -9550,7 +9550,7 @@
         <v>46486</v>
       </c>
       <c r="CR25" t="str">
-        <v>(614) 897-8705</v>
+        <v>(614) 555-0111</v>
       </c>
       <c r="CS25" t="str">
         <v>Dr. Ramon Ortiz</v>
@@ -9666,22 +9666,22 @@
         <v>Priya Patel</v>
       </c>
       <c r="C26" t="str">
-        <v>2200 Superior Ave, Cleveland, OH 44114</v>
+        <v>520 Demo Street, Cleveland, OH 44114</v>
       </c>
       <c r="D26" t="str">
-        <v>359-469-5960</v>
+        <v>359-555-0100</v>
       </c>
       <c r="E26" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="F26" t="str">
         <v>Chase</v>
       </c>
       <c r="G26">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H26">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I26" t="str">
         <v>summary</v>
@@ -9690,7 +9690,7 @@
         <v>VALID</v>
       </c>
       <c r="K26" t="str">
-        <v>OH9775880</v>
+        <v>OH0000149</v>
       </c>
       <c r="L26">
         <v>46739</v>
@@ -9717,7 +9717,7 @@
         <v>F</v>
       </c>
       <c r="U26">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V26" t="str">
         <v>DRV-004.png</v>
@@ -9726,10 +9726,10 @@
         <v>South Asian</v>
       </c>
       <c r="X26" t="str">
-        <v>priyapatel@yahoo.com</v>
+        <v>priyapatel@example.com</v>
       </c>
       <c r="Y26" t="str">
-        <v>2200 Superior Ave</v>
+        <v>520 Demo Street</v>
       </c>
       <c r="Z26" t="str">
         <v>Cleveland</v>
@@ -9810,7 +9810,7 @@
         <v>SSN</v>
       </c>
       <c r="BD26" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="BF26">
         <v>45432</v>
@@ -9903,7 +9903,7 @@
         <v>Patel</v>
       </c>
       <c r="CL26" t="str">
-        <v>OH8493499</v>
+        <v>OH0000133</v>
       </c>
       <c r="CM26" t="str">
         <v>OH</v>
@@ -9921,7 +9921,7 @@
         <v>46486</v>
       </c>
       <c r="CR26" t="str">
-        <v>(614) 897-8705</v>
+        <v>(614) 555-0111</v>
       </c>
       <c r="CS26" t="str">
         <v>Dr. Ramon Ortiz</v>
@@ -10037,22 +10037,22 @@
         <v>Priya Patel</v>
       </c>
       <c r="C27" t="str">
-        <v>2200 Superior Ave, Cleveland, OH 44114</v>
+        <v>520 Demo Street, Cleveland, OH 44114</v>
       </c>
       <c r="D27" t="str">
-        <v>359-469-5960</v>
+        <v>359-555-0100</v>
       </c>
       <c r="E27" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="F27" t="str">
         <v>Chase</v>
       </c>
       <c r="G27">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H27">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I27" t="str">
         <v>Road Test Certificate</v>
@@ -10061,7 +10061,7 @@
         <v>VALID</v>
       </c>
       <c r="K27" t="str">
-        <v>OH1046362</v>
+        <v>OH0000072</v>
       </c>
       <c r="L27">
         <v>46739</v>
@@ -10088,7 +10088,7 @@
         <v>F</v>
       </c>
       <c r="U27">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V27" t="str">
         <v>DRV-004.png</v>
@@ -10097,10 +10097,10 @@
         <v>South Asian</v>
       </c>
       <c r="X27" t="str">
-        <v>priyapatel@yahoo.com</v>
+        <v>priyapatel@example.com</v>
       </c>
       <c r="Y27" t="str">
-        <v>2200 Superior Ave</v>
+        <v>520 Demo Street</v>
       </c>
       <c r="Z27" t="str">
         <v>Cleveland</v>
@@ -10181,7 +10181,7 @@
         <v>SSN</v>
       </c>
       <c r="BD27" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="BF27">
         <v>45432</v>
@@ -10274,7 +10274,7 @@
         <v>Patel</v>
       </c>
       <c r="CL27" t="str">
-        <v>OH8493500</v>
+        <v>OH0000134</v>
       </c>
       <c r="CM27" t="str">
         <v>OH</v>
@@ -10292,7 +10292,7 @@
         <v>46486</v>
       </c>
       <c r="CR27" t="str">
-        <v>(614) 897-8705</v>
+        <v>(614) 555-0111</v>
       </c>
       <c r="CS27" t="str">
         <v>Dr. Ramon Ortiz</v>
@@ -10408,22 +10408,22 @@
         <v>Priya Patel</v>
       </c>
       <c r="C28" t="str">
-        <v>2200 Superior Ave, Cleveland, OH 44114</v>
+        <v>520 Demo Street, Cleveland, OH 44114</v>
       </c>
       <c r="D28" t="str">
-        <v>359-469-5960</v>
+        <v>359-555-0100</v>
       </c>
       <c r="E28" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="F28" t="str">
         <v>Chase</v>
       </c>
       <c r="G28">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H28">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I28" t="str">
         <v>Incident/Accident Report</v>
@@ -10432,7 +10432,7 @@
         <v>VALID</v>
       </c>
       <c r="K28" t="str">
-        <v>OH1138650</v>
+        <v>OH0000074</v>
       </c>
       <c r="L28">
         <v>46739</v>
@@ -10462,7 +10462,7 @@
         <v>F</v>
       </c>
       <c r="U28">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V28" t="str">
         <v>DRV-004.png</v>
@@ -10471,10 +10471,10 @@
         <v>South Asian</v>
       </c>
       <c r="X28" t="str">
-        <v>priyapatel@yahoo.com</v>
+        <v>priyapatel@example.com</v>
       </c>
       <c r="Y28" t="str">
-        <v>2200 Superior Ave</v>
+        <v>520 Demo Street</v>
       </c>
       <c r="Z28" t="str">
         <v>Cleveland</v>
@@ -10555,7 +10555,7 @@
         <v>SSN</v>
       </c>
       <c r="BD28" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="BF28">
         <v>45432</v>
@@ -10648,7 +10648,7 @@
         <v>Patel</v>
       </c>
       <c r="CL28" t="str">
-        <v>OH8493501</v>
+        <v>OH0000135</v>
       </c>
       <c r="CM28" t="str">
         <v>OH</v>
@@ -10666,7 +10666,7 @@
         <v>46486</v>
       </c>
       <c r="CR28" t="str">
-        <v>(614) 897-8705</v>
+        <v>(614) 555-0111</v>
       </c>
       <c r="CS28" t="str">
         <v>Dr. Ramon Ortiz</v>
@@ -10782,22 +10782,22 @@
         <v>Priya Patel</v>
       </c>
       <c r="C29" t="str">
-        <v>2200 Superior Ave, Cleveland, OH 44114</v>
+        <v>520 Demo Street, Cleveland, OH 44114</v>
       </c>
       <c r="D29" t="str">
-        <v>359-469-5960</v>
+        <v>359-555-0100</v>
       </c>
       <c r="E29" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="F29" t="str">
         <v>Chase</v>
       </c>
       <c r="G29">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H29">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I29" t="str">
         <v>Direct Deposit Form</v>
@@ -10806,7 +10806,7 @@
         <v>VALID</v>
       </c>
       <c r="K29" t="str">
-        <v>OH4059570</v>
+        <v>OH0000095</v>
       </c>
       <c r="L29">
         <v>46739</v>
@@ -10833,7 +10833,7 @@
         <v>F</v>
       </c>
       <c r="U29">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V29" t="str">
         <v>DRV-004.png</v>
@@ -10842,10 +10842,10 @@
         <v>South Asian</v>
       </c>
       <c r="X29" t="str">
-        <v>priyapatel@yahoo.com</v>
+        <v>priyapatel@example.com</v>
       </c>
       <c r="Y29" t="str">
-        <v>2200 Superior Ave</v>
+        <v>520 Demo Street</v>
       </c>
       <c r="Z29" t="str">
         <v>Cleveland</v>
@@ -10926,7 +10926,7 @@
         <v>SSN</v>
       </c>
       <c r="BD29" t="str">
-        <v>***-**-8257</v>
+        <v>***-**-0119</v>
       </c>
       <c r="BF29">
         <v>45432</v>
@@ -11019,7 +11019,7 @@
         <v>Patel</v>
       </c>
       <c r="CL29" t="str">
-        <v>OH8493502</v>
+        <v>OH0000136</v>
       </c>
       <c r="CM29" t="str">
         <v>OH</v>
@@ -11037,7 +11037,7 @@
         <v>46486</v>
       </c>
       <c r="CR29" t="str">
-        <v>(614) 897-8705</v>
+        <v>(614) 555-0111</v>
       </c>
       <c r="CS29" t="str">
         <v>Dr. Ramon Ortiz</v>
@@ -11153,22 +11153,22 @@
         <v>Kenji Tanaka</v>
       </c>
       <c r="C30" t="str">
-        <v>115 E Broad St, Columbus, OH 43215</v>
+        <v>150 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D30" t="str">
-        <v>871-429-6220</v>
+        <v>871-555-0100</v>
       </c>
       <c r="E30" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="F30" t="str">
         <v>Chase</v>
       </c>
       <c r="G30">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H30">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I30" t="str">
         <v>CDL Summary</v>
@@ -11177,7 +11177,7 @@
         <v>VALID</v>
       </c>
       <c r="K30" t="str">
-        <v>OH2779041</v>
+        <v>OH0000084</v>
       </c>
       <c r="L30">
         <v>46577</v>
@@ -11204,7 +11204,7 @@
         <v>M</v>
       </c>
       <c r="U30">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V30" t="str">
         <v>DRV-005.png</v>
@@ -11213,10 +11213,10 @@
         <v>Asian</v>
       </c>
       <c r="X30" t="str">
-        <v>ktanaka@yahoo.com</v>
+        <v>ktanaka@example.com</v>
       </c>
       <c r="Y30" t="str">
-        <v>115 E Broad St</v>
+        <v>150 Demo Street</v>
       </c>
       <c r="Z30" t="str">
         <v>Columbus</v>
@@ -11300,7 +11300,7 @@
         <v>SSN</v>
       </c>
       <c r="BD30" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="BF30">
         <v>45509</v>
@@ -11393,7 +11393,7 @@
         <v>Tanaka</v>
       </c>
       <c r="CL30" t="str">
-        <v>OH2779041</v>
+        <v>OH0000084</v>
       </c>
       <c r="CM30" t="str">
         <v>OH</v>
@@ -11411,7 +11411,7 @@
         <v>46496</v>
       </c>
       <c r="CR30" t="str">
-        <v>(614) 806-7535</v>
+        <v>(614) 555-0106</v>
       </c>
       <c r="CS30" t="str">
         <v>Dr. Helen Price</v>
@@ -11527,22 +11527,22 @@
         <v>Kenji Tanaka</v>
       </c>
       <c r="C31" t="str">
-        <v>115 E Broad St, Columbus, OH 43215</v>
+        <v>150 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D31" t="str">
-        <v>871-429-6220</v>
+        <v>871-555-0100</v>
       </c>
       <c r="E31" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="F31" t="str">
         <v>Chase</v>
       </c>
       <c r="G31">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H31">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I31" t="str">
         <v>Medical Certification</v>
@@ -11551,7 +11551,7 @@
         <v>VALID</v>
       </c>
       <c r="K31" t="str">
-        <v>OH3434069</v>
+        <v>OH0000093</v>
       </c>
       <c r="L31">
         <v>46577</v>
@@ -11578,7 +11578,7 @@
         <v>M</v>
       </c>
       <c r="U31">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V31" t="str">
         <v>DRV-005.png</v>
@@ -11587,10 +11587,10 @@
         <v>Asian</v>
       </c>
       <c r="X31" t="str">
-        <v>ktanaka@yahoo.com</v>
+        <v>ktanaka@example.com</v>
       </c>
       <c r="Y31" t="str">
-        <v>115 E Broad St</v>
+        <v>150 Demo Street</v>
       </c>
       <c r="Z31" t="str">
         <v>Columbus</v>
@@ -11674,7 +11674,7 @@
         <v>SSN</v>
       </c>
       <c r="BD31" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="BF31">
         <v>45509</v>
@@ -11767,7 +11767,7 @@
         <v>Tanaka</v>
       </c>
       <c r="CL31" t="str">
-        <v>OH2779042</v>
+        <v>OH0000085</v>
       </c>
       <c r="CM31" t="str">
         <v>OH</v>
@@ -11785,7 +11785,7 @@
         <v>46496</v>
       </c>
       <c r="CR31" t="str">
-        <v>(614) 806-7535</v>
+        <v>(614) 555-0106</v>
       </c>
       <c r="CS31" t="str">
         <v>Dr. Helen Price</v>
@@ -11901,22 +11901,22 @@
         <v>Kenji Tanaka</v>
       </c>
       <c r="C32" t="str">
-        <v>115 E Broad St, Columbus, OH 43215</v>
+        <v>150 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D32" t="str">
-        <v>871-429-6220</v>
+        <v>871-555-0100</v>
       </c>
       <c r="E32" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="F32" t="str">
         <v>Chase</v>
       </c>
       <c r="G32">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H32">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I32" t="str">
         <v>MVR Background Report</v>
@@ -11925,7 +11925,7 @@
         <v>VALID</v>
       </c>
       <c r="K32" t="str">
-        <v>OH6720716</v>
+        <v>OH0000119</v>
       </c>
       <c r="L32">
         <v>46577</v>
@@ -11952,7 +11952,7 @@
         <v>M</v>
       </c>
       <c r="U32">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V32" t="str">
         <v>DRV-005.png</v>
@@ -11961,10 +11961,10 @@
         <v>Asian</v>
       </c>
       <c r="X32" t="str">
-        <v>ktanaka@yahoo.com</v>
+        <v>ktanaka@example.com</v>
       </c>
       <c r="Y32" t="str">
-        <v>115 E Broad St</v>
+        <v>150 Demo Street</v>
       </c>
       <c r="Z32" t="str">
         <v>Columbus</v>
@@ -12048,7 +12048,7 @@
         <v>SSN</v>
       </c>
       <c r="BD32" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="BF32">
         <v>45509</v>
@@ -12141,7 +12141,7 @@
         <v>Tanaka</v>
       </c>
       <c r="CL32" t="str">
-        <v>OH2779043</v>
+        <v>OH0000086</v>
       </c>
       <c r="CM32" t="str">
         <v>OH</v>
@@ -12159,7 +12159,7 @@
         <v>46496</v>
       </c>
       <c r="CR32" t="str">
-        <v>(614) 806-7535</v>
+        <v>(614) 555-0106</v>
       </c>
       <c r="CS32" t="str">
         <v>Dr. Helen Price</v>
@@ -12275,22 +12275,22 @@
         <v>Kenji Tanaka</v>
       </c>
       <c r="C33" t="str">
-        <v>115 E Broad St, Columbus, OH 43215</v>
+        <v>150 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D33" t="str">
-        <v>871-429-6220</v>
+        <v>871-555-0100</v>
       </c>
       <c r="E33" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="F33" t="str">
         <v>Chase</v>
       </c>
       <c r="G33">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H33">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I33" t="str">
         <v>Driver Application</v>
@@ -12299,7 +12299,7 @@
         <v>VALID</v>
       </c>
       <c r="K33" t="str">
-        <v>OH5640312</v>
+        <v>OH0000102</v>
       </c>
       <c r="L33">
         <v>46577</v>
@@ -12326,7 +12326,7 @@
         <v>M</v>
       </c>
       <c r="U33">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V33" t="str">
         <v>DRV-005.png</v>
@@ -12335,10 +12335,10 @@
         <v>Asian</v>
       </c>
       <c r="X33" t="str">
-        <v>ktanaka@yahoo.com</v>
+        <v>ktanaka@example.com</v>
       </c>
       <c r="Y33" t="str">
-        <v>115 E Broad St</v>
+        <v>150 Demo Street</v>
       </c>
       <c r="Z33" t="str">
         <v>Columbus</v>
@@ -12422,7 +12422,7 @@
         <v>SSN</v>
       </c>
       <c r="BD33" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="BF33">
         <v>45509</v>
@@ -12515,7 +12515,7 @@
         <v>Tanaka</v>
       </c>
       <c r="CL33" t="str">
-        <v>OH2779044</v>
+        <v>OH0000087</v>
       </c>
       <c r="CM33" t="str">
         <v>OH</v>
@@ -12533,7 +12533,7 @@
         <v>46496</v>
       </c>
       <c r="CR33" t="str">
-        <v>(614) 806-7535</v>
+        <v>(614) 555-0106</v>
       </c>
       <c r="CS33" t="str">
         <v>Dr. Helen Price</v>
@@ -12649,22 +12649,22 @@
         <v>Kenji Tanaka</v>
       </c>
       <c r="C34" t="str">
-        <v>115 E Broad St, Columbus, OH 43215</v>
+        <v>150 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D34" t="str">
-        <v>871-429-6220</v>
+        <v>871-555-0100</v>
       </c>
       <c r="E34" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="F34" t="str">
         <v>Chase</v>
       </c>
       <c r="G34">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H34">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I34" t="str">
         <v>Road Test Certificate</v>
@@ -12673,7 +12673,7 @@
         <v>VALID</v>
       </c>
       <c r="K34" t="str">
-        <v>OH7627072</v>
+        <v>OH0000125</v>
       </c>
       <c r="L34">
         <v>46577</v>
@@ -12700,7 +12700,7 @@
         <v>M</v>
       </c>
       <c r="U34">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V34" t="str">
         <v>DRV-005.png</v>
@@ -12709,10 +12709,10 @@
         <v>Asian</v>
       </c>
       <c r="X34" t="str">
-        <v>ktanaka@yahoo.com</v>
+        <v>ktanaka@example.com</v>
       </c>
       <c r="Y34" t="str">
-        <v>115 E Broad St</v>
+        <v>150 Demo Street</v>
       </c>
       <c r="Z34" t="str">
         <v>Columbus</v>
@@ -12796,7 +12796,7 @@
         <v>SSN</v>
       </c>
       <c r="BD34" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="BF34">
         <v>45509</v>
@@ -12889,7 +12889,7 @@
         <v>Tanaka</v>
       </c>
       <c r="CL34" t="str">
-        <v>OH2779045</v>
+        <v>OH0000088</v>
       </c>
       <c r="CM34" t="str">
         <v>OH</v>
@@ -12907,7 +12907,7 @@
         <v>46496</v>
       </c>
       <c r="CR34" t="str">
-        <v>(614) 806-7535</v>
+        <v>(614) 555-0106</v>
       </c>
       <c r="CS34" t="str">
         <v>Dr. Helen Price</v>
@@ -13023,22 +13023,22 @@
         <v>Kenji Tanaka</v>
       </c>
       <c r="C35" t="str">
-        <v>115 E Broad St, Columbus, OH 43215</v>
+        <v>150 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D35" t="str">
-        <v>871-429-6220</v>
+        <v>871-555-0100</v>
       </c>
       <c r="E35" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="F35" t="str">
         <v>Chase</v>
       </c>
       <c r="G35">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H35">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I35" t="str">
         <v>Incident/Accident Report</v>
@@ -13047,7 +13047,7 @@
         <v>VALID</v>
       </c>
       <c r="K35" t="str">
-        <v>OH1919210</v>
+        <v>OH0000082</v>
       </c>
       <c r="L35">
         <v>46577</v>
@@ -13077,7 +13077,7 @@
         <v>M</v>
       </c>
       <c r="U35">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V35" t="str">
         <v>DRV-005.png</v>
@@ -13086,10 +13086,10 @@
         <v>Asian</v>
       </c>
       <c r="X35" t="str">
-        <v>ktanaka@yahoo.com</v>
+        <v>ktanaka@example.com</v>
       </c>
       <c r="Y35" t="str">
-        <v>115 E Broad St</v>
+        <v>150 Demo Street</v>
       </c>
       <c r="Z35" t="str">
         <v>Columbus</v>
@@ -13173,7 +13173,7 @@
         <v>SSN</v>
       </c>
       <c r="BD35" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="BF35">
         <v>45509</v>
@@ -13266,7 +13266,7 @@
         <v>Tanaka</v>
       </c>
       <c r="CL35" t="str">
-        <v>OH2779046</v>
+        <v>OH0000089</v>
       </c>
       <c r="CM35" t="str">
         <v>OH</v>
@@ -13284,7 +13284,7 @@
         <v>46496</v>
       </c>
       <c r="CR35" t="str">
-        <v>(614) 806-7535</v>
+        <v>(614) 555-0106</v>
       </c>
       <c r="CS35" t="str">
         <v>Dr. Helen Price</v>
@@ -13400,22 +13400,22 @@
         <v>Kenji Tanaka</v>
       </c>
       <c r="C36" t="str">
-        <v>115 E Broad St, Columbus, OH 43215</v>
+        <v>150 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D36" t="str">
-        <v>871-429-6220</v>
+        <v>871-555-0100</v>
       </c>
       <c r="E36" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="F36" t="str">
         <v>Chase</v>
       </c>
       <c r="G36">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H36">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I36" t="str">
         <v>Direct Deposit Form</v>
@@ -13424,7 +13424,7 @@
         <v>VALID</v>
       </c>
       <c r="K36" t="str">
-        <v>OH7765263</v>
+        <v>OH0000126</v>
       </c>
       <c r="L36">
         <v>46577</v>
@@ -13451,7 +13451,7 @@
         <v>M</v>
       </c>
       <c r="U36">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V36" t="str">
         <v>DRV-005.png</v>
@@ -13460,10 +13460,10 @@
         <v>Asian</v>
       </c>
       <c r="X36" t="str">
-        <v>ktanaka@yahoo.com</v>
+        <v>ktanaka@example.com</v>
       </c>
       <c r="Y36" t="str">
-        <v>115 E Broad St</v>
+        <v>150 Demo Street</v>
       </c>
       <c r="Z36" t="str">
         <v>Columbus</v>
@@ -13547,7 +13547,7 @@
         <v>SSN</v>
       </c>
       <c r="BD36" t="str">
-        <v>***-**-1789</v>
+        <v>***-**-0102</v>
       </c>
       <c r="BF36">
         <v>45509</v>
@@ -13640,7 +13640,7 @@
         <v>Tanaka</v>
       </c>
       <c r="CL36" t="str">
-        <v>OH2779047</v>
+        <v>OH0000090</v>
       </c>
       <c r="CM36" t="str">
         <v>OH</v>
@@ -13658,7 +13658,7 @@
         <v>46496</v>
       </c>
       <c r="CR36" t="str">
-        <v>(614) 806-7535</v>
+        <v>(614) 555-0106</v>
       </c>
       <c r="CS36" t="str">
         <v>Dr. Helen Price</v>
@@ -13774,22 +13774,22 @@
         <v>Marcus Chen</v>
       </c>
       <c r="C37" t="str">
-        <v>500 Pacific Ave, Dallas, TX 75202</v>
+        <v>810 Demo Street, Dallas, TX 75202</v>
       </c>
       <c r="D37" t="str">
-        <v>283-876-4322</v>
+        <v>283-555-0100</v>
       </c>
       <c r="E37" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="F37" t="str">
         <v>Chase</v>
       </c>
       <c r="G37">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H37">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I37" t="str">
         <v>CDL Summary</v>
@@ -13798,7 +13798,7 @@
         <v>VALID</v>
       </c>
       <c r="K37" t="str">
-        <v>TX3261112</v>
+        <v>TX0000158</v>
       </c>
       <c r="L37">
         <v>45826</v>
@@ -13825,7 +13825,7 @@
         <v>M</v>
       </c>
       <c r="U37">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V37" t="str">
         <v>DRV-006.png</v>
@@ -13834,10 +13834,10 @@
         <v>Asian</v>
       </c>
       <c r="X37" t="str">
-        <v>mchen@hotmail.com</v>
+        <v>mchen@example.com</v>
       </c>
       <c r="Y37" t="str">
-        <v>500 Pacific Ave</v>
+        <v>810 Demo Street</v>
       </c>
       <c r="Z37" t="str">
         <v>Dallas</v>
@@ -13912,7 +13912,7 @@
         <v>SSN</v>
       </c>
       <c r="BD37" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="BF37">
         <v>45544</v>
@@ -14005,7 +14005,7 @@
         <v>Chen</v>
       </c>
       <c r="CL37" t="str">
-        <v>TX3261112</v>
+        <v>TX0000158</v>
       </c>
       <c r="CM37" t="str">
         <v>TX</v>
@@ -14023,7 +14023,7 @@
         <v>46394</v>
       </c>
       <c r="CR37" t="str">
-        <v>(512) 621-2178</v>
+        <v>(512) 555-0100</v>
       </c>
       <c r="CS37" t="str">
         <v>Dr. Monica Steele</v>
@@ -14139,22 +14139,22 @@
         <v>Marcus Chen</v>
       </c>
       <c r="C38" t="str">
-        <v>500 Pacific Ave, Dallas, TX 75202</v>
+        <v>810 Demo Street, Dallas, TX 75202</v>
       </c>
       <c r="D38" t="str">
-        <v>283-876-4322</v>
+        <v>283-555-0100</v>
       </c>
       <c r="E38" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="F38" t="str">
         <v>Chase</v>
       </c>
       <c r="G38">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H38">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I38" t="str">
         <v>Medical Certification</v>
@@ -14163,7 +14163,7 @@
         <v>VALID</v>
       </c>
       <c r="K38" t="str">
-        <v>TX3531641</v>
+        <v>TX0000165</v>
       </c>
       <c r="L38">
         <v>45826</v>
@@ -14190,7 +14190,7 @@
         <v>M</v>
       </c>
       <c r="U38">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V38" t="str">
         <v>DRV-006.png</v>
@@ -14199,10 +14199,10 @@
         <v>Asian</v>
       </c>
       <c r="X38" t="str">
-        <v>mchen@hotmail.com</v>
+        <v>mchen@example.com</v>
       </c>
       <c r="Y38" t="str">
-        <v>500 Pacific Ave</v>
+        <v>810 Demo Street</v>
       </c>
       <c r="Z38" t="str">
         <v>Dallas</v>
@@ -14277,7 +14277,7 @@
         <v>SSN</v>
       </c>
       <c r="BD38" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="BF38">
         <v>45544</v>
@@ -14370,7 +14370,7 @@
         <v>Chen</v>
       </c>
       <c r="CL38" t="str">
-        <v>TX3261113</v>
+        <v>TX0000159</v>
       </c>
       <c r="CM38" t="str">
         <v>TX</v>
@@ -14388,7 +14388,7 @@
         <v>46394</v>
       </c>
       <c r="CR38" t="str">
-        <v>(512) 621-2178</v>
+        <v>(512) 555-0100</v>
       </c>
       <c r="CS38" t="str">
         <v>Dr. Monica Steele</v>
@@ -14504,22 +14504,22 @@
         <v>Marcus Chen</v>
       </c>
       <c r="C39" t="str">
-        <v>500 Pacific Ave, Dallas, TX 75202</v>
+        <v>810 Demo Street, Dallas, TX 75202</v>
       </c>
       <c r="D39" t="str">
-        <v>283-876-4322</v>
+        <v>283-555-0100</v>
       </c>
       <c r="E39" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="F39" t="str">
         <v>Chase</v>
       </c>
       <c r="G39">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H39">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I39" t="str">
         <v>MVR Background Report</v>
@@ -14528,7 +14528,7 @@
         <v>VALID</v>
       </c>
       <c r="K39" t="str">
-        <v>TX2647879</v>
+        <v>TX0000155</v>
       </c>
       <c r="L39">
         <v>45826</v>
@@ -14555,7 +14555,7 @@
         <v>M</v>
       </c>
       <c r="U39">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V39" t="str">
         <v>DRV-006.png</v>
@@ -14564,10 +14564,10 @@
         <v>Asian</v>
       </c>
       <c r="X39" t="str">
-        <v>mchen@hotmail.com</v>
+        <v>mchen@example.com</v>
       </c>
       <c r="Y39" t="str">
-        <v>500 Pacific Ave</v>
+        <v>810 Demo Street</v>
       </c>
       <c r="Z39" t="str">
         <v>Dallas</v>
@@ -14642,7 +14642,7 @@
         <v>SSN</v>
       </c>
       <c r="BD39" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="BF39">
         <v>45544</v>
@@ -14735,7 +14735,7 @@
         <v>Chen</v>
       </c>
       <c r="CL39" t="str">
-        <v>TX3261114</v>
+        <v>TX0000160</v>
       </c>
       <c r="CM39" t="str">
         <v>TX</v>
@@ -14753,7 +14753,7 @@
         <v>46394</v>
       </c>
       <c r="CR39" t="str">
-        <v>(512) 621-2178</v>
+        <v>(512) 555-0100</v>
       </c>
       <c r="CS39" t="str">
         <v>Dr. Monica Steele</v>
@@ -14869,22 +14869,22 @@
         <v>Marcus Chen</v>
       </c>
       <c r="C40" t="str">
-        <v>500 Pacific Ave, Dallas, TX 75202</v>
+        <v>810 Demo Street, Dallas, TX 75202</v>
       </c>
       <c r="D40" t="str">
-        <v>283-876-4322</v>
+        <v>283-555-0100</v>
       </c>
       <c r="E40" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="F40" t="str">
         <v>Chase</v>
       </c>
       <c r="G40">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H40">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I40" t="str">
         <v>Driver Application</v>
@@ -14893,7 +14893,7 @@
         <v>VALID</v>
       </c>
       <c r="K40" t="str">
-        <v>TX3779357</v>
+        <v>TX0000166</v>
       </c>
       <c r="L40">
         <v>45826</v>
@@ -14920,7 +14920,7 @@
         <v>M</v>
       </c>
       <c r="U40">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V40" t="str">
         <v>DRV-006.png</v>
@@ -14929,10 +14929,10 @@
         <v>Asian</v>
       </c>
       <c r="X40" t="str">
-        <v>mchen@hotmail.com</v>
+        <v>mchen@example.com</v>
       </c>
       <c r="Y40" t="str">
-        <v>500 Pacific Ave</v>
+        <v>810 Demo Street</v>
       </c>
       <c r="Z40" t="str">
         <v>Dallas</v>
@@ -15007,7 +15007,7 @@
         <v>SSN</v>
       </c>
       <c r="BD40" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="BF40">
         <v>45544</v>
@@ -15100,7 +15100,7 @@
         <v>Chen</v>
       </c>
       <c r="CL40" t="str">
-        <v>TX3261115</v>
+        <v>TX0000161</v>
       </c>
       <c r="CM40" t="str">
         <v>TX</v>
@@ -15118,7 +15118,7 @@
         <v>46394</v>
       </c>
       <c r="CR40" t="str">
-        <v>(512) 621-2178</v>
+        <v>(512) 555-0100</v>
       </c>
       <c r="CS40" t="str">
         <v>Dr. Monica Steele</v>
@@ -15234,22 +15234,22 @@
         <v>Marcus Chen</v>
       </c>
       <c r="C41" t="str">
-        <v>500 Pacific Ave, Dallas, TX 75202</v>
+        <v>810 Demo Street, Dallas, TX 75202</v>
       </c>
       <c r="D41" t="str">
-        <v>283-876-4322</v>
+        <v>283-555-0100</v>
       </c>
       <c r="E41" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="F41" t="str">
         <v>Chase</v>
       </c>
       <c r="G41">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H41">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I41" t="str">
         <v>Road Test Certificate</v>
@@ -15258,7 +15258,7 @@
         <v>VALID</v>
       </c>
       <c r="K41" t="str">
-        <v>TX3175879</v>
+        <v>TX0000156</v>
       </c>
       <c r="L41">
         <v>45826</v>
@@ -15285,7 +15285,7 @@
         <v>M</v>
       </c>
       <c r="U41">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V41" t="str">
         <v>DRV-006.png</v>
@@ -15294,10 +15294,10 @@
         <v>Asian</v>
       </c>
       <c r="X41" t="str">
-        <v>mchen@hotmail.com</v>
+        <v>mchen@example.com</v>
       </c>
       <c r="Y41" t="str">
-        <v>500 Pacific Ave</v>
+        <v>810 Demo Street</v>
       </c>
       <c r="Z41" t="str">
         <v>Dallas</v>
@@ -15372,7 +15372,7 @@
         <v>SSN</v>
       </c>
       <c r="BD41" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="BF41">
         <v>45544</v>
@@ -15465,7 +15465,7 @@
         <v>Chen</v>
       </c>
       <c r="CL41" t="str">
-        <v>TX3261116</v>
+        <v>TX0000162</v>
       </c>
       <c r="CM41" t="str">
         <v>TX</v>
@@ -15483,7 +15483,7 @@
         <v>46394</v>
       </c>
       <c r="CR41" t="str">
-        <v>(512) 621-2178</v>
+        <v>(512) 555-0100</v>
       </c>
       <c r="CS41" t="str">
         <v>Dr. Monica Steele</v>
@@ -15599,22 +15599,22 @@
         <v>Marcus Chen</v>
       </c>
       <c r="C42" t="str">
-        <v>500 Pacific Ave, Dallas, TX 75202</v>
+        <v>810 Demo Street, Dallas, TX 75202</v>
       </c>
       <c r="D42" t="str">
-        <v>283-876-4322</v>
+        <v>283-555-0100</v>
       </c>
       <c r="E42" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="F42" t="str">
         <v>Chase</v>
       </c>
       <c r="G42">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H42">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I42" t="str">
         <v>Incident/Accident Report</v>
@@ -15623,7 +15623,7 @@
         <v>VALID</v>
       </c>
       <c r="K42" t="str">
-        <v>TX8659153</v>
+        <v>TX0000167</v>
       </c>
       <c r="L42">
         <v>45826</v>
@@ -15653,7 +15653,7 @@
         <v>M</v>
       </c>
       <c r="U42">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V42" t="str">
         <v>DRV-006.png</v>
@@ -15662,10 +15662,10 @@
         <v>Asian</v>
       </c>
       <c r="X42" t="str">
-        <v>mchen@hotmail.com</v>
+        <v>mchen@example.com</v>
       </c>
       <c r="Y42" t="str">
-        <v>500 Pacific Ave</v>
+        <v>810 Demo Street</v>
       </c>
       <c r="Z42" t="str">
         <v>Dallas</v>
@@ -15740,7 +15740,7 @@
         <v>SSN</v>
       </c>
       <c r="BD42" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="BF42">
         <v>45544</v>
@@ -15833,7 +15833,7 @@
         <v>Chen</v>
       </c>
       <c r="CL42" t="str">
-        <v>TX3261117</v>
+        <v>TX0000163</v>
       </c>
       <c r="CM42" t="str">
         <v>TX</v>
@@ -15851,7 +15851,7 @@
         <v>46394</v>
       </c>
       <c r="CR42" t="str">
-        <v>(512) 621-2178</v>
+        <v>(512) 555-0100</v>
       </c>
       <c r="CS42" t="str">
         <v>Dr. Monica Steele</v>
@@ -15967,22 +15967,22 @@
         <v>Marcus Chen</v>
       </c>
       <c r="C43" t="str">
-        <v>500 Pacific Ave, Dallas, TX 75202</v>
+        <v>810 Demo Street, Dallas, TX 75202</v>
       </c>
       <c r="D43" t="str">
-        <v>283-876-4322</v>
+        <v>283-555-0100</v>
       </c>
       <c r="E43" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="F43" t="str">
         <v>Chase</v>
       </c>
       <c r="G43">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H43">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I43" t="str">
         <v>Direct Deposit Form</v>
@@ -15991,7 +15991,7 @@
         <v>VALID</v>
       </c>
       <c r="K43" t="str">
-        <v>TX3212501</v>
+        <v>TX0000157</v>
       </c>
       <c r="L43">
         <v>45826</v>
@@ -16018,7 +16018,7 @@
         <v>M</v>
       </c>
       <c r="U43">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V43" t="str">
         <v>DRV-006.png</v>
@@ -16027,10 +16027,10 @@
         <v>Asian</v>
       </c>
       <c r="X43" t="str">
-        <v>mchen@hotmail.com</v>
+        <v>mchen@example.com</v>
       </c>
       <c r="Y43" t="str">
-        <v>500 Pacific Ave</v>
+        <v>810 Demo Street</v>
       </c>
       <c r="Z43" t="str">
         <v>Dallas</v>
@@ -16105,7 +16105,7 @@
         <v>SSN</v>
       </c>
       <c r="BD43" t="str">
-        <v>***-**-1521</v>
+        <v>***-**-0101</v>
       </c>
       <c r="BF43">
         <v>45544</v>
@@ -16198,7 +16198,7 @@
         <v>Chen</v>
       </c>
       <c r="CL43" t="str">
-        <v>TX3261118</v>
+        <v>TX0000164</v>
       </c>
       <c r="CM43" t="str">
         <v>TX</v>
@@ -16216,7 +16216,7 @@
         <v>46394</v>
       </c>
       <c r="CR43" t="str">
-        <v>(512) 621-2178</v>
+        <v>(512) 555-0100</v>
       </c>
       <c r="CS43" t="str">
         <v>Dr. Monica Steele</v>
@@ -16332,22 +16332,22 @@
         <v>Sofia Gomez</v>
       </c>
       <c r="C44" t="str">
-        <v>815 Prospect Ave, Cleveland, OH 44115</v>
+        <v>1020 Demo Street, Cleveland, OH 44115</v>
       </c>
       <c r="D44" t="str">
-        <v>896-828-7164</v>
+        <v>896-555-0100</v>
       </c>
       <c r="E44" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="F44" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G44">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H44">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I44" t="str">
         <v>CDL Summary</v>
@@ -16356,7 +16356,7 @@
         <v>VALID</v>
       </c>
       <c r="K44" t="str">
-        <v>OH6635833</v>
+        <v>OH0000112</v>
       </c>
       <c r="L44">
         <v>46530</v>
@@ -16383,7 +16383,7 @@
         <v>F</v>
       </c>
       <c r="U44">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V44" t="str">
         <v>DRV-007.png</v>
@@ -16392,10 +16392,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X44" t="str">
-        <v>sofiagomez@yahoo.com</v>
+        <v>sofiagomez@example.com</v>
       </c>
       <c r="Y44" t="str">
-        <v>815 Prospect Ave</v>
+        <v>1020 Demo Street</v>
       </c>
       <c r="Z44" t="str">
         <v>Cleveland</v>
@@ -16470,7 +16470,7 @@
         <v>SSN</v>
       </c>
       <c r="BD44" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="BF44">
         <v>45566</v>
@@ -16557,7 +16557,7 @@
         <v>Gomez</v>
       </c>
       <c r="CL44" t="str">
-        <v>OH6635833</v>
+        <v>OH0000112</v>
       </c>
       <c r="CM44" t="str">
         <v>OH</v>
@@ -16575,7 +16575,7 @@
         <v>45739</v>
       </c>
       <c r="CR44" t="str">
-        <v>(614) 574-7480</v>
+        <v>(614) 555-0105</v>
       </c>
       <c r="CS44" t="str">
         <v>Dr. James Carter</v>
@@ -16691,22 +16691,22 @@
         <v>Sofia Gomez</v>
       </c>
       <c r="C45" t="str">
-        <v>815 Prospect Ave, Cleveland, OH 44115</v>
+        <v>1020 Demo Street, Cleveland, OH 44115</v>
       </c>
       <c r="D45" t="str">
-        <v>896-828-7164</v>
+        <v>896-555-0100</v>
       </c>
       <c r="E45" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="F45" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G45">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H45">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I45" t="str">
         <v>Medical Certification</v>
@@ -16715,7 +16715,7 @@
         <v>VALID</v>
       </c>
       <c r="K45" t="str">
-        <v>OH6094308</v>
+        <v>OH0000103</v>
       </c>
       <c r="L45">
         <v>46530</v>
@@ -16742,7 +16742,7 @@
         <v>F</v>
       </c>
       <c r="U45">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V45" t="str">
         <v>DRV-007.png</v>
@@ -16751,10 +16751,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X45" t="str">
-        <v>sofiagomez@yahoo.com</v>
+        <v>sofiagomez@example.com</v>
       </c>
       <c r="Y45" t="str">
-        <v>815 Prospect Ave</v>
+        <v>1020 Demo Street</v>
       </c>
       <c r="Z45" t="str">
         <v>Cleveland</v>
@@ -16829,7 +16829,7 @@
         <v>SSN</v>
       </c>
       <c r="BD45" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="BF45">
         <v>45566</v>
@@ -16916,7 +16916,7 @@
         <v>Gomez</v>
       </c>
       <c r="CL45" t="str">
-        <v>OH6635834</v>
+        <v>OH0000113</v>
       </c>
       <c r="CM45" t="str">
         <v>OH</v>
@@ -16934,7 +16934,7 @@
         <v>45739</v>
       </c>
       <c r="CR45" t="str">
-        <v>(614) 574-7480</v>
+        <v>(614) 555-0105</v>
       </c>
       <c r="CS45" t="str">
         <v>Dr. James Carter</v>
@@ -17050,22 +17050,22 @@
         <v>Sofia Gomez</v>
       </c>
       <c r="C46" t="str">
-        <v>815 Prospect Ave, Cleveland, OH 44115</v>
+        <v>1020 Demo Street, Cleveland, OH 44115</v>
       </c>
       <c r="D46" t="str">
-        <v>896-828-7164</v>
+        <v>896-555-0100</v>
       </c>
       <c r="E46" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="F46" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G46">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H46">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I46" t="str">
         <v>MVR Background Report</v>
@@ -17074,7 +17074,7 @@
         <v>VALID</v>
       </c>
       <c r="K46" t="str">
-        <v>OH5247055</v>
+        <v>OH0000101</v>
       </c>
       <c r="L46">
         <v>46530</v>
@@ -17101,7 +17101,7 @@
         <v>F</v>
       </c>
       <c r="U46">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V46" t="str">
         <v>DRV-007.png</v>
@@ -17110,10 +17110,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X46" t="str">
-        <v>sofiagomez@yahoo.com</v>
+        <v>sofiagomez@example.com</v>
       </c>
       <c r="Y46" t="str">
-        <v>815 Prospect Ave</v>
+        <v>1020 Demo Street</v>
       </c>
       <c r="Z46" t="str">
         <v>Cleveland</v>
@@ -17188,7 +17188,7 @@
         <v>SSN</v>
       </c>
       <c r="BD46" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="BF46">
         <v>45566</v>
@@ -17275,7 +17275,7 @@
         <v>Gomez</v>
       </c>
       <c r="CL46" t="str">
-        <v>OH6635835</v>
+        <v>OH0000114</v>
       </c>
       <c r="CM46" t="str">
         <v>OH</v>
@@ -17293,7 +17293,7 @@
         <v>45739</v>
       </c>
       <c r="CR46" t="str">
-        <v>(614) 574-7480</v>
+        <v>(614) 555-0105</v>
       </c>
       <c r="CS46" t="str">
         <v>Dr. James Carter</v>
@@ -17409,22 +17409,22 @@
         <v>Sofia Gomez</v>
       </c>
       <c r="C47" t="str">
-        <v>815 Prospect Ave, Cleveland, OH 44115</v>
+        <v>1020 Demo Street, Cleveland, OH 44115</v>
       </c>
       <c r="D47" t="str">
-        <v>896-828-7164</v>
+        <v>896-555-0100</v>
       </c>
       <c r="E47" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="F47" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G47">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H47">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I47" t="str">
         <v>Driver Application</v>
@@ -17433,7 +17433,7 @@
         <v>VALID</v>
       </c>
       <c r="K47" t="str">
-        <v>OH8453480</v>
+        <v>OH0000129</v>
       </c>
       <c r="L47">
         <v>46530</v>
@@ -17460,7 +17460,7 @@
         <v>F</v>
       </c>
       <c r="U47">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V47" t="str">
         <v>DRV-007.png</v>
@@ -17469,10 +17469,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X47" t="str">
-        <v>sofiagomez@yahoo.com</v>
+        <v>sofiagomez@example.com</v>
       </c>
       <c r="Y47" t="str">
-        <v>815 Prospect Ave</v>
+        <v>1020 Demo Street</v>
       </c>
       <c r="Z47" t="str">
         <v>Cleveland</v>
@@ -17547,7 +17547,7 @@
         <v>SSN</v>
       </c>
       <c r="BD47" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="BF47">
         <v>45566</v>
@@ -17634,7 +17634,7 @@
         <v>Gomez</v>
       </c>
       <c r="CL47" t="str">
-        <v>OH6635836</v>
+        <v>OH0000115</v>
       </c>
       <c r="CM47" t="str">
         <v>OH</v>
@@ -17652,7 +17652,7 @@
         <v>45739</v>
       </c>
       <c r="CR47" t="str">
-        <v>(614) 574-7480</v>
+        <v>(614) 555-0105</v>
       </c>
       <c r="CS47" t="str">
         <v>Dr. James Carter</v>
@@ -17768,22 +17768,22 @@
         <v>Sofia Gomez</v>
       </c>
       <c r="C48" t="str">
-        <v>815 Prospect Ave, Cleveland, OH 44115</v>
+        <v>1020 Demo Street, Cleveland, OH 44115</v>
       </c>
       <c r="D48" t="str">
-        <v>896-828-7164</v>
+        <v>896-555-0100</v>
       </c>
       <c r="E48" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="F48" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G48">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H48">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I48" t="str">
         <v>Road Test Certificate</v>
@@ -17792,7 +17792,7 @@
         <v>VALID</v>
       </c>
       <c r="K48" t="str">
-        <v>OH6843221</v>
+        <v>OH0000120</v>
       </c>
       <c r="L48">
         <v>46530</v>
@@ -17819,7 +17819,7 @@
         <v>F</v>
       </c>
       <c r="U48">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V48" t="str">
         <v>DRV-007.png</v>
@@ -17828,10 +17828,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X48" t="str">
-        <v>sofiagomez@yahoo.com</v>
+        <v>sofiagomez@example.com</v>
       </c>
       <c r="Y48" t="str">
-        <v>815 Prospect Ave</v>
+        <v>1020 Demo Street</v>
       </c>
       <c r="Z48" t="str">
         <v>Cleveland</v>
@@ -17906,7 +17906,7 @@
         <v>SSN</v>
       </c>
       <c r="BD48" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="BF48">
         <v>45566</v>
@@ -17993,7 +17993,7 @@
         <v>Gomez</v>
       </c>
       <c r="CL48" t="str">
-        <v>OH6635837</v>
+        <v>OH0000116</v>
       </c>
       <c r="CM48" t="str">
         <v>OH</v>
@@ -18011,7 +18011,7 @@
         <v>45739</v>
       </c>
       <c r="CR48" t="str">
-        <v>(614) 574-7480</v>
+        <v>(614) 555-0105</v>
       </c>
       <c r="CS48" t="str">
         <v>Dr. James Carter</v>
@@ -18127,22 +18127,22 @@
         <v>Sofia Gomez</v>
       </c>
       <c r="C49" t="str">
-        <v>815 Prospect Ave, Cleveland, OH 44115</v>
+        <v>1020 Demo Street, Cleveland, OH 44115</v>
       </c>
       <c r="D49" t="str">
-        <v>896-828-7164</v>
+        <v>896-555-0100</v>
       </c>
       <c r="E49" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="F49" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G49">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H49">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I49" t="str">
         <v>Incident/Accident Report</v>
@@ -18151,7 +18151,7 @@
         <v>VALID</v>
       </c>
       <c r="K49" t="str">
-        <v>OH6877493</v>
+        <v>OH0000121</v>
       </c>
       <c r="L49">
         <v>46530</v>
@@ -18181,7 +18181,7 @@
         <v>F</v>
       </c>
       <c r="U49">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V49" t="str">
         <v>DRV-007.png</v>
@@ -18190,10 +18190,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X49" t="str">
-        <v>sofiagomez@yahoo.com</v>
+        <v>sofiagomez@example.com</v>
       </c>
       <c r="Y49" t="str">
-        <v>815 Prospect Ave</v>
+        <v>1020 Demo Street</v>
       </c>
       <c r="Z49" t="str">
         <v>Cleveland</v>
@@ -18268,7 +18268,7 @@
         <v>SSN</v>
       </c>
       <c r="BD49" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="BF49">
         <v>45566</v>
@@ -18355,7 +18355,7 @@
         <v>Gomez</v>
       </c>
       <c r="CL49" t="str">
-        <v>OH6635838</v>
+        <v>OH0000117</v>
       </c>
       <c r="CM49" t="str">
         <v>OH</v>
@@ -18373,7 +18373,7 @@
         <v>45739</v>
       </c>
       <c r="CR49" t="str">
-        <v>(614) 574-7480</v>
+        <v>(614) 555-0105</v>
       </c>
       <c r="CS49" t="str">
         <v>Dr. James Carter</v>
@@ -18489,22 +18489,22 @@
         <v>Sofia Gomez</v>
       </c>
       <c r="C50" t="str">
-        <v>815 Prospect Ave, Cleveland, OH 44115</v>
+        <v>1020 Demo Street, Cleveland, OH 44115</v>
       </c>
       <c r="D50" t="str">
-        <v>896-828-7164</v>
+        <v>896-555-0100</v>
       </c>
       <c r="E50" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="F50" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G50">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H50">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I50" t="str">
         <v>Direct Deposit Form</v>
@@ -18513,7 +18513,7 @@
         <v>VALID</v>
       </c>
       <c r="K50" t="str">
-        <v>OH1110710</v>
+        <v>OH0000073</v>
       </c>
       <c r="L50">
         <v>46530</v>
@@ -18540,7 +18540,7 @@
         <v>F</v>
       </c>
       <c r="U50">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V50" t="str">
         <v>DRV-007.png</v>
@@ -18549,10 +18549,10 @@
         <v>Hispanic</v>
       </c>
       <c r="X50" t="str">
-        <v>sofiagomez@yahoo.com</v>
+        <v>sofiagomez@example.com</v>
       </c>
       <c r="Y50" t="str">
-        <v>815 Prospect Ave</v>
+        <v>1020 Demo Street</v>
       </c>
       <c r="Z50" t="str">
         <v>Cleveland</v>
@@ -18627,7 +18627,7 @@
         <v>SSN</v>
       </c>
       <c r="BD50" t="str">
-        <v>***-**-4815</v>
+        <v>***-**-0109</v>
       </c>
       <c r="BF50">
         <v>45566</v>
@@ -18714,7 +18714,7 @@
         <v>Gomez</v>
       </c>
       <c r="CL50" t="str">
-        <v>OH6635839</v>
+        <v>OH0000118</v>
       </c>
       <c r="CM50" t="str">
         <v>OH</v>
@@ -18732,7 +18732,7 @@
         <v>45739</v>
       </c>
       <c r="CR50" t="str">
-        <v>(614) 574-7480</v>
+        <v>(614) 555-0105</v>
       </c>
       <c r="CS50" t="str">
         <v>Dr. James Carter</v>
@@ -18848,22 +18848,22 @@
         <v>Liam Smith</v>
       </c>
       <c r="C51" t="str">
-        <v>240 Madison Ave, Toledo, OH 43604</v>
+        <v>530 Demo Street, Toledo, OH 43604</v>
       </c>
       <c r="D51" t="str">
-        <v>820-223-4829</v>
+        <v>820-555-0100</v>
       </c>
       <c r="E51" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="F51" t="str">
         <v>PNC</v>
       </c>
       <c r="G51">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H51">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I51" t="str">
         <v>CDL Summary</v>
@@ -18872,7 +18872,7 @@
         <v>VALID</v>
       </c>
       <c r="K51" t="str">
-        <v>OH9450480</v>
+        <v>OH0000141</v>
       </c>
       <c r="L51">
         <v>46620</v>
@@ -18899,7 +18899,7 @@
         <v>M</v>
       </c>
       <c r="U51">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V51" t="str">
         <v>DRV-008.png</v>
@@ -18908,10 +18908,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X51" t="str">
-        <v>liamsmith@gmail.com</v>
+        <v>liamsmith@example.com</v>
       </c>
       <c r="Y51" t="str">
-        <v>240 Madison Ave</v>
+        <v>530 Demo Street</v>
       </c>
       <c r="Z51" t="str">
         <v>Toledo</v>
@@ -18995,7 +18995,7 @@
         <v>SSN</v>
       </c>
       <c r="BD51" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="BF51">
         <v>45467</v>
@@ -19088,7 +19088,7 @@
         <v>Smith</v>
       </c>
       <c r="CL51" t="str">
-        <v>OH9450480</v>
+        <v>OH0000141</v>
       </c>
       <c r="CM51" t="str">
         <v>OH</v>
@@ -19106,7 +19106,7 @@
         <v>46670</v>
       </c>
       <c r="CR51" t="str">
-        <v>(614) 937-6329</v>
+        <v>(614) 555-0114</v>
       </c>
       <c r="CS51" t="str">
         <v>Dr. Alicia Brooks</v>
@@ -19222,22 +19222,22 @@
         <v>Liam Smith</v>
       </c>
       <c r="C52" t="str">
-        <v>240 Madison Ave, Toledo, OH 43604</v>
+        <v>530 Demo Street, Toledo, OH 43604</v>
       </c>
       <c r="D52" t="str">
-        <v>820-223-4829</v>
+        <v>820-555-0100</v>
       </c>
       <c r="E52" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="F52" t="str">
         <v>PNC</v>
       </c>
       <c r="G52">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H52">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I52" t="str">
         <v>Medical Certification</v>
@@ -19246,7 +19246,7 @@
         <v>VALID</v>
       </c>
       <c r="K52" t="str">
-        <v>OH8889985</v>
+        <v>OH0000139</v>
       </c>
       <c r="L52">
         <v>46620</v>
@@ -19273,7 +19273,7 @@
         <v>M</v>
       </c>
       <c r="U52">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V52" t="str">
         <v>DRV-008.png</v>
@@ -19282,10 +19282,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X52" t="str">
-        <v>liamsmith@gmail.com</v>
+        <v>liamsmith@example.com</v>
       </c>
       <c r="Y52" t="str">
-        <v>240 Madison Ave</v>
+        <v>530 Demo Street</v>
       </c>
       <c r="Z52" t="str">
         <v>Toledo</v>
@@ -19369,7 +19369,7 @@
         <v>SSN</v>
       </c>
       <c r="BD52" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="BF52">
         <v>45467</v>
@@ -19462,7 +19462,7 @@
         <v>Smith</v>
       </c>
       <c r="CL52" t="str">
-        <v>OH9450481</v>
+        <v>OH0000142</v>
       </c>
       <c r="CM52" t="str">
         <v>OH</v>
@@ -19480,7 +19480,7 @@
         <v>46670</v>
       </c>
       <c r="CR52" t="str">
-        <v>(614) 937-6329</v>
+        <v>(614) 555-0114</v>
       </c>
       <c r="CS52" t="str">
         <v>Dr. Alicia Brooks</v>
@@ -19596,22 +19596,22 @@
         <v>Liam Smith</v>
       </c>
       <c r="C53" t="str">
-        <v>240 Madison Ave, Toledo, OH 43604</v>
+        <v>530 Demo Street, Toledo, OH 43604</v>
       </c>
       <c r="D53" t="str">
-        <v>820-223-4829</v>
+        <v>820-555-0100</v>
       </c>
       <c r="E53" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="F53" t="str">
         <v>PNC</v>
       </c>
       <c r="G53">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H53">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I53" t="str">
         <v>MVR Background Report</v>
@@ -19620,7 +19620,7 @@
         <v>VALID</v>
       </c>
       <c r="K53" t="str">
-        <v>OH2899009</v>
+        <v>OH0000091</v>
       </c>
       <c r="L53">
         <v>46620</v>
@@ -19647,7 +19647,7 @@
         <v>M</v>
       </c>
       <c r="U53">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V53" t="str">
         <v>DRV-008.png</v>
@@ -19656,10 +19656,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X53" t="str">
-        <v>liamsmith@gmail.com</v>
+        <v>liamsmith@example.com</v>
       </c>
       <c r="Y53" t="str">
-        <v>240 Madison Ave</v>
+        <v>530 Demo Street</v>
       </c>
       <c r="Z53" t="str">
         <v>Toledo</v>
@@ -19743,7 +19743,7 @@
         <v>SSN</v>
       </c>
       <c r="BD53" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="BF53">
         <v>45467</v>
@@ -19836,7 +19836,7 @@
         <v>Smith</v>
       </c>
       <c r="CL53" t="str">
-        <v>OH9450482</v>
+        <v>OH0000143</v>
       </c>
       <c r="CM53" t="str">
         <v>OH</v>
@@ -19854,7 +19854,7 @@
         <v>46670</v>
       </c>
       <c r="CR53" t="str">
-        <v>(614) 937-6329</v>
+        <v>(614) 555-0114</v>
       </c>
       <c r="CS53" t="str">
         <v>Dr. Alicia Brooks</v>
@@ -19970,22 +19970,22 @@
         <v>Liam Smith</v>
       </c>
       <c r="C54" t="str">
-        <v>240 Madison Ave, Toledo, OH 43604</v>
+        <v>530 Demo Street, Toledo, OH 43604</v>
       </c>
       <c r="D54" t="str">
-        <v>820-223-4829</v>
+        <v>820-555-0100</v>
       </c>
       <c r="E54" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="F54" t="str">
         <v>PNC</v>
       </c>
       <c r="G54">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H54">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I54" t="str">
         <v>Driver Application</v>
@@ -19994,7 +19994,7 @@
         <v>VALID</v>
       </c>
       <c r="K54" t="str">
-        <v>OH8294998</v>
+        <v>OH0000128</v>
       </c>
       <c r="L54">
         <v>46620</v>
@@ -20021,7 +20021,7 @@
         <v>M</v>
       </c>
       <c r="U54">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V54" t="str">
         <v>DRV-008.png</v>
@@ -20030,10 +20030,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X54" t="str">
-        <v>liamsmith@gmail.com</v>
+        <v>liamsmith@example.com</v>
       </c>
       <c r="Y54" t="str">
-        <v>240 Madison Ave</v>
+        <v>530 Demo Street</v>
       </c>
       <c r="Z54" t="str">
         <v>Toledo</v>
@@ -20117,7 +20117,7 @@
         <v>SSN</v>
       </c>
       <c r="BD54" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="BF54">
         <v>45467</v>
@@ -20210,7 +20210,7 @@
         <v>Smith</v>
       </c>
       <c r="CL54" t="str">
-        <v>OH9450483</v>
+        <v>OH0000144</v>
       </c>
       <c r="CM54" t="str">
         <v>OH</v>
@@ -20228,7 +20228,7 @@
         <v>46670</v>
       </c>
       <c r="CR54" t="str">
-        <v>(614) 937-6329</v>
+        <v>(614) 555-0114</v>
       </c>
       <c r="CS54" t="str">
         <v>Dr. Alicia Brooks</v>
@@ -20344,22 +20344,22 @@
         <v>Liam Smith</v>
       </c>
       <c r="C55" t="str">
-        <v>240 Madison Ave, Toledo, OH 43604</v>
+        <v>530 Demo Street, Toledo, OH 43604</v>
       </c>
       <c r="D55" t="str">
-        <v>820-223-4829</v>
+        <v>820-555-0100</v>
       </c>
       <c r="E55" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="F55" t="str">
         <v>PNC</v>
       </c>
       <c r="G55">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H55">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I55" t="str">
         <v>Road Test Certificate</v>
@@ -20368,7 +20368,7 @@
         <v>VALID</v>
       </c>
       <c r="K55" t="str">
-        <v>OH3539286</v>
+        <v>OH0000094</v>
       </c>
       <c r="L55">
         <v>46620</v>
@@ -20395,7 +20395,7 @@
         <v>M</v>
       </c>
       <c r="U55">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V55" t="str">
         <v>DRV-008.png</v>
@@ -20404,10 +20404,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X55" t="str">
-        <v>liamsmith@gmail.com</v>
+        <v>liamsmith@example.com</v>
       </c>
       <c r="Y55" t="str">
-        <v>240 Madison Ave</v>
+        <v>530 Demo Street</v>
       </c>
       <c r="Z55" t="str">
         <v>Toledo</v>
@@ -20491,7 +20491,7 @@
         <v>SSN</v>
       </c>
       <c r="BD55" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="BF55">
         <v>45467</v>
@@ -20584,7 +20584,7 @@
         <v>Smith</v>
       </c>
       <c r="CL55" t="str">
-        <v>OH9450484</v>
+        <v>OH0000145</v>
       </c>
       <c r="CM55" t="str">
         <v>OH</v>
@@ -20602,7 +20602,7 @@
         <v>46670</v>
       </c>
       <c r="CR55" t="str">
-        <v>(614) 937-6329</v>
+        <v>(614) 555-0114</v>
       </c>
       <c r="CS55" t="str">
         <v>Dr. Alicia Brooks</v>
@@ -20718,22 +20718,22 @@
         <v>Liam Smith</v>
       </c>
       <c r="C56" t="str">
-        <v>240 Madison Ave, Toledo, OH 43604</v>
+        <v>530 Demo Street, Toledo, OH 43604</v>
       </c>
       <c r="D56" t="str">
-        <v>820-223-4829</v>
+        <v>820-555-0100</v>
       </c>
       <c r="E56" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="F56" t="str">
         <v>PNC</v>
       </c>
       <c r="G56">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H56">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I56" t="str">
         <v>Incident/Accident Report</v>
@@ -20742,7 +20742,7 @@
         <v>VALID</v>
       </c>
       <c r="K56" t="str">
-        <v>OH4520738</v>
+        <v>OH0000098</v>
       </c>
       <c r="L56">
         <v>46620</v>
@@ -20772,7 +20772,7 @@
         <v>M</v>
       </c>
       <c r="U56">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V56" t="str">
         <v>DRV-008.png</v>
@@ -20781,10 +20781,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X56" t="str">
-        <v>liamsmith@gmail.com</v>
+        <v>liamsmith@example.com</v>
       </c>
       <c r="Y56" t="str">
-        <v>240 Madison Ave</v>
+        <v>530 Demo Street</v>
       </c>
       <c r="Z56" t="str">
         <v>Toledo</v>
@@ -20868,7 +20868,7 @@
         <v>SSN</v>
       </c>
       <c r="BD56" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="BF56">
         <v>45467</v>
@@ -20961,7 +20961,7 @@
         <v>Smith</v>
       </c>
       <c r="CL56" t="str">
-        <v>OH9450485</v>
+        <v>OH0000146</v>
       </c>
       <c r="CM56" t="str">
         <v>OH</v>
@@ -20979,7 +20979,7 @@
         <v>46670</v>
       </c>
       <c r="CR56" t="str">
-        <v>(614) 937-6329</v>
+        <v>(614) 555-0114</v>
       </c>
       <c r="CS56" t="str">
         <v>Dr. Alicia Brooks</v>
@@ -21095,22 +21095,22 @@
         <v>Liam Smith</v>
       </c>
       <c r="C57" t="str">
-        <v>240 Madison Ave, Toledo, OH 43604</v>
+        <v>530 Demo Street, Toledo, OH 43604</v>
       </c>
       <c r="D57" t="str">
-        <v>820-223-4829</v>
+        <v>820-555-0100</v>
       </c>
       <c r="E57" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="F57" t="str">
         <v>PNC</v>
       </c>
       <c r="G57">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H57">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I57" t="str">
         <v>Direct Deposit Form</v>
@@ -21119,7 +21119,7 @@
         <v>VALID</v>
       </c>
       <c r="K57" t="str">
-        <v>OH9851872</v>
+        <v>OH0000150</v>
       </c>
       <c r="L57">
         <v>46620</v>
@@ -21146,7 +21146,7 @@
         <v>M</v>
       </c>
       <c r="U57">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V57" t="str">
         <v>DRV-008.png</v>
@@ -21155,10 +21155,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X57" t="str">
-        <v>liamsmith@gmail.com</v>
+        <v>liamsmith@example.com</v>
       </c>
       <c r="Y57" t="str">
-        <v>240 Madison Ave</v>
+        <v>530 Demo Street</v>
       </c>
       <c r="Z57" t="str">
         <v>Toledo</v>
@@ -21242,7 +21242,7 @@
         <v>SSN</v>
       </c>
       <c r="BD57" t="str">
-        <v>***-**-4800</v>
+        <v>***-**-0108</v>
       </c>
       <c r="BF57">
         <v>45467</v>
@@ -21335,7 +21335,7 @@
         <v>Smith</v>
       </c>
       <c r="CL57" t="str">
-        <v>OH9450486</v>
+        <v>OH0000147</v>
       </c>
       <c r="CM57" t="str">
         <v>OH</v>
@@ -21353,7 +21353,7 @@
         <v>46670</v>
       </c>
       <c r="CR57" t="str">
-        <v>(614) 937-6329</v>
+        <v>(614) 555-0114</v>
       </c>
       <c r="CS57" t="str">
         <v>Dr. Alicia Brooks</v>
@@ -21469,22 +21469,22 @@
         <v>Emma Brown</v>
       </c>
       <c r="C58" t="str">
-        <v>330 Civic Center Dr, Columbus, OH 43215</v>
+        <v>630 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D58" t="str">
-        <v>206-700-7666</v>
+        <v>206-555-0103</v>
       </c>
       <c r="E58" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="F58" t="str">
         <v>Chase</v>
       </c>
       <c r="G58">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H58">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I58" t="str">
         <v>CDL Summary</v>
@@ -21493,7 +21493,7 @@
         <v>VALID</v>
       </c>
       <c r="K58" t="str">
-        <v>OH6116714</v>
+        <v>OH0000104</v>
       </c>
       <c r="L58">
         <v>46424</v>
@@ -21520,7 +21520,7 @@
         <v>F</v>
       </c>
       <c r="U58">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V58" t="str">
         <v>DRV-009.png</v>
@@ -21529,10 +21529,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X58" t="str">
-        <v>emmabrown@yahoo.com</v>
+        <v>emmabrown@example.com</v>
       </c>
       <c r="Y58" t="str">
-        <v>330 Civic Center Dr</v>
+        <v>630 Demo Street</v>
       </c>
       <c r="Z58" t="str">
         <v>Columbus</v>
@@ -21613,7 +21613,7 @@
         <v>SSN</v>
       </c>
       <c r="BD58" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="BF58">
         <v>45502</v>
@@ -21703,7 +21703,7 @@
         <v>Brown</v>
       </c>
       <c r="CL58" t="str">
-        <v>OH6116714</v>
+        <v>OH0000104</v>
       </c>
       <c r="CM58" t="str">
         <v>OH</v>
@@ -21721,7 +21721,7 @@
         <v>46645</v>
       </c>
       <c r="CR58" t="str">
-        <v>(614) 935-8132</v>
+        <v>(614) 555-0113</v>
       </c>
       <c r="CS58" t="str">
         <v>Dr. David Yang</v>
@@ -21837,22 +21837,22 @@
         <v>Emma Brown</v>
       </c>
       <c r="C59" t="str">
-        <v>330 Civic Center Dr, Columbus, OH 43215</v>
+        <v>630 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D59" t="str">
-        <v>206-700-7666</v>
+        <v>206-555-0103</v>
       </c>
       <c r="E59" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="F59" t="str">
         <v>Chase</v>
       </c>
       <c r="G59">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H59">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I59" t="str">
         <v>Medical Certification</v>
@@ -21861,7 +21861,7 @@
         <v>VALID</v>
       </c>
       <c r="K59" t="str">
-        <v>OH2742151</v>
+        <v>OH0000083</v>
       </c>
       <c r="L59">
         <v>46424</v>
@@ -21888,7 +21888,7 @@
         <v>F</v>
       </c>
       <c r="U59">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V59" t="str">
         <v>DRV-009.png</v>
@@ -21897,10 +21897,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X59" t="str">
-        <v>emmabrown@yahoo.com</v>
+        <v>emmabrown@example.com</v>
       </c>
       <c r="Y59" t="str">
-        <v>330 Civic Center Dr</v>
+        <v>630 Demo Street</v>
       </c>
       <c r="Z59" t="str">
         <v>Columbus</v>
@@ -21981,7 +21981,7 @@
         <v>SSN</v>
       </c>
       <c r="BD59" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="BF59">
         <v>45502</v>
@@ -22071,7 +22071,7 @@
         <v>Brown</v>
       </c>
       <c r="CL59" t="str">
-        <v>OH6116715</v>
+        <v>OH0000105</v>
       </c>
       <c r="CM59" t="str">
         <v>OH</v>
@@ -22089,7 +22089,7 @@
         <v>46645</v>
       </c>
       <c r="CR59" t="str">
-        <v>(614) 935-8132</v>
+        <v>(614) 555-0113</v>
       </c>
       <c r="CS59" t="str">
         <v>Dr. David Yang</v>
@@ -22205,22 +22205,22 @@
         <v>Emma Brown</v>
       </c>
       <c r="C60" t="str">
-        <v>330 Civic Center Dr, Columbus, OH 43215</v>
+        <v>630 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D60" t="str">
-        <v>206-700-7666</v>
+        <v>206-555-0103</v>
       </c>
       <c r="E60" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="F60" t="str">
         <v>Chase</v>
       </c>
       <c r="G60">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H60">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I60" t="str">
         <v>MVR Background Report</v>
@@ -22229,7 +22229,7 @@
         <v>VALID</v>
       </c>
       <c r="K60" t="str">
-        <v>OH5031927</v>
+        <v>OH0000100</v>
       </c>
       <c r="L60">
         <v>46424</v>
@@ -22256,7 +22256,7 @@
         <v>F</v>
       </c>
       <c r="U60">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V60" t="str">
         <v>DRV-009.png</v>
@@ -22265,10 +22265,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X60" t="str">
-        <v>emmabrown@yahoo.com</v>
+        <v>emmabrown@example.com</v>
       </c>
       <c r="Y60" t="str">
-        <v>330 Civic Center Dr</v>
+        <v>630 Demo Street</v>
       </c>
       <c r="Z60" t="str">
         <v>Columbus</v>
@@ -22349,7 +22349,7 @@
         <v>SSN</v>
       </c>
       <c r="BD60" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="BF60">
         <v>45502</v>
@@ -22439,7 +22439,7 @@
         <v>Brown</v>
       </c>
       <c r="CL60" t="str">
-        <v>OH6116716</v>
+        <v>OH0000106</v>
       </c>
       <c r="CM60" t="str">
         <v>OH</v>
@@ -22457,7 +22457,7 @@
         <v>46645</v>
       </c>
       <c r="CR60" t="str">
-        <v>(614) 935-8132</v>
+        <v>(614) 555-0113</v>
       </c>
       <c r="CS60" t="str">
         <v>Dr. David Yang</v>
@@ -22573,22 +22573,22 @@
         <v>Emma Brown</v>
       </c>
       <c r="C61" t="str">
-        <v>330 Civic Center Dr, Columbus, OH 43215</v>
+        <v>630 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D61" t="str">
-        <v>206-700-7666</v>
+        <v>206-555-0103</v>
       </c>
       <c r="E61" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="F61" t="str">
         <v>Chase</v>
       </c>
       <c r="G61">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H61">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I61" t="str">
         <v>Driver Application</v>
@@ -22597,7 +22597,7 @@
         <v>VALID</v>
       </c>
       <c r="K61" t="str">
-        <v>OH9570143</v>
+        <v>OH0000148</v>
       </c>
       <c r="L61">
         <v>46424</v>
@@ -22624,7 +22624,7 @@
         <v>F</v>
       </c>
       <c r="U61">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V61" t="str">
         <v>DRV-009.png</v>
@@ -22633,10 +22633,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X61" t="str">
-        <v>emmabrown@yahoo.com</v>
+        <v>emmabrown@example.com</v>
       </c>
       <c r="Y61" t="str">
-        <v>330 Civic Center Dr</v>
+        <v>630 Demo Street</v>
       </c>
       <c r="Z61" t="str">
         <v>Columbus</v>
@@ -22717,7 +22717,7 @@
         <v>SSN</v>
       </c>
       <c r="BD61" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="BF61">
         <v>45502</v>
@@ -22807,7 +22807,7 @@
         <v>Brown</v>
       </c>
       <c r="CL61" t="str">
-        <v>OH6116717</v>
+        <v>OH0000107</v>
       </c>
       <c r="CM61" t="str">
         <v>OH</v>
@@ -22825,7 +22825,7 @@
         <v>46645</v>
       </c>
       <c r="CR61" t="str">
-        <v>(614) 935-8132</v>
+        <v>(614) 555-0113</v>
       </c>
       <c r="CS61" t="str">
         <v>Dr. David Yang</v>
@@ -22941,22 +22941,22 @@
         <v>Emma Brown</v>
       </c>
       <c r="C62" t="str">
-        <v>330 Civic Center Dr, Columbus, OH 43215</v>
+        <v>630 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D62" t="str">
-        <v>206-700-7666</v>
+        <v>206-555-0103</v>
       </c>
       <c r="E62" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="F62" t="str">
         <v>Chase</v>
       </c>
       <c r="G62">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H62">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I62" t="str">
         <v>Road Test Certificate</v>
@@ -22965,7 +22965,7 @@
         <v>VALID</v>
       </c>
       <c r="K62" t="str">
-        <v>OH7265424</v>
+        <v>OH0000122</v>
       </c>
       <c r="L62">
         <v>46424</v>
@@ -22992,7 +22992,7 @@
         <v>F</v>
       </c>
       <c r="U62">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V62" t="str">
         <v>DRV-009.png</v>
@@ -23001,10 +23001,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X62" t="str">
-        <v>emmabrown@yahoo.com</v>
+        <v>emmabrown@example.com</v>
       </c>
       <c r="Y62" t="str">
-        <v>330 Civic Center Dr</v>
+        <v>630 Demo Street</v>
       </c>
       <c r="Z62" t="str">
         <v>Columbus</v>
@@ -23085,7 +23085,7 @@
         <v>SSN</v>
       </c>
       <c r="BD62" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="BF62">
         <v>45502</v>
@@ -23175,7 +23175,7 @@
         <v>Brown</v>
       </c>
       <c r="CL62" t="str">
-        <v>OH6116718</v>
+        <v>OH0000108</v>
       </c>
       <c r="CM62" t="str">
         <v>OH</v>
@@ -23193,7 +23193,7 @@
         <v>46645</v>
       </c>
       <c r="CR62" t="str">
-        <v>(614) 935-8132</v>
+        <v>(614) 555-0113</v>
       </c>
       <c r="CS62" t="str">
         <v>Dr. David Yang</v>
@@ -23309,22 +23309,22 @@
         <v>Emma Brown</v>
       </c>
       <c r="C63" t="str">
-        <v>330 Civic Center Dr, Columbus, OH 43215</v>
+        <v>630 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D63" t="str">
-        <v>206-700-7666</v>
+        <v>206-555-0103</v>
       </c>
       <c r="E63" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="F63" t="str">
         <v>Chase</v>
       </c>
       <c r="G63">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H63">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I63" t="str">
         <v>Incident/Accident Report</v>
@@ -23333,7 +23333,7 @@
         <v>VALID</v>
       </c>
       <c r="K63" t="str">
-        <v>OH4179820</v>
+        <v>OH0000096</v>
       </c>
       <c r="L63">
         <v>46424</v>
@@ -23363,7 +23363,7 @@
         <v>F</v>
       </c>
       <c r="U63">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V63" t="str">
         <v>DRV-009.png</v>
@@ -23372,10 +23372,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X63" t="str">
-        <v>emmabrown@yahoo.com</v>
+        <v>emmabrown@example.com</v>
       </c>
       <c r="Y63" t="str">
-        <v>330 Civic Center Dr</v>
+        <v>630 Demo Street</v>
       </c>
       <c r="Z63" t="str">
         <v>Columbus</v>
@@ -23456,7 +23456,7 @@
         <v>SSN</v>
       </c>
       <c r="BD63" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="BF63">
         <v>45502</v>
@@ -23546,7 +23546,7 @@
         <v>Brown</v>
       </c>
       <c r="CL63" t="str">
-        <v>OH6116719</v>
+        <v>OH0000109</v>
       </c>
       <c r="CM63" t="str">
         <v>OH</v>
@@ -23564,7 +23564,7 @@
         <v>46645</v>
       </c>
       <c r="CR63" t="str">
-        <v>(614) 935-8132</v>
+        <v>(614) 555-0113</v>
       </c>
       <c r="CS63" t="str">
         <v>Dr. David Yang</v>
@@ -23680,22 +23680,22 @@
         <v>Emma Brown</v>
       </c>
       <c r="C64" t="str">
-        <v>330 Civic Center Dr, Columbus, OH 43215</v>
+        <v>630 Demo Street, Columbus, OH 43215</v>
       </c>
       <c r="D64" t="str">
-        <v>206-700-7666</v>
+        <v>206-555-0103</v>
       </c>
       <c r="E64" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="F64" t="str">
         <v>Chase</v>
       </c>
       <c r="G64">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H64">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I64" t="str">
         <v>Direct Deposit Form</v>
@@ -23704,7 +23704,7 @@
         <v>VALID</v>
       </c>
       <c r="K64" t="str">
-        <v>OH9306784</v>
+        <v>OH0000140</v>
       </c>
       <c r="L64">
         <v>46424</v>
@@ -23731,7 +23731,7 @@
         <v>F</v>
       </c>
       <c r="U64">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V64" t="str">
         <v>DRV-009.png</v>
@@ -23740,10 +23740,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X64" t="str">
-        <v>emmabrown@yahoo.com</v>
+        <v>emmabrown@example.com</v>
       </c>
       <c r="Y64" t="str">
-        <v>330 Civic Center Dr</v>
+        <v>630 Demo Street</v>
       </c>
       <c r="Z64" t="str">
         <v>Columbus</v>
@@ -23824,7 +23824,7 @@
         <v>SSN</v>
       </c>
       <c r="BD64" t="str">
-        <v>***-**-9930</v>
+        <v>***-**-0124</v>
       </c>
       <c r="BF64">
         <v>45502</v>
@@ -23914,7 +23914,7 @@
         <v>Brown</v>
       </c>
       <c r="CL64" t="str">
-        <v>OH6116720</v>
+        <v>OH0000110</v>
       </c>
       <c r="CM64" t="str">
         <v>OH</v>
@@ -23932,7 +23932,7 @@
         <v>46645</v>
       </c>
       <c r="CR64" t="str">
-        <v>(614) 935-8132</v>
+        <v>(614) 555-0113</v>
       </c>
       <c r="CS64" t="str">
         <v>Dr. David Yang</v>
@@ -24048,22 +24048,22 @@
         <v>Noah Wilson</v>
       </c>
       <c r="C65" t="str">
-        <v>110 W Adams St, Chicago, IL 60603</v>
+        <v>130 Demo Street, Chicago, IL 60603</v>
       </c>
       <c r="D65" t="str">
-        <v>582-987-2387</v>
+        <v>582-555-0100</v>
       </c>
       <c r="E65" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="F65" t="str">
         <v>Chase</v>
       </c>
       <c r="G65">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H65">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I65" t="str">
         <v>CDL Summary</v>
@@ -24072,7 +24072,7 @@
         <v>VALID</v>
       </c>
       <c r="K65" t="str">
-        <v>IL3858215</v>
+        <v>IL0000049</v>
       </c>
       <c r="L65">
         <v>46647</v>
@@ -24099,7 +24099,7 @@
         <v>M</v>
       </c>
       <c r="U65">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V65" t="str">
         <v>DRV-010.png</v>
@@ -24108,10 +24108,10 @@
         <v>Black</v>
       </c>
       <c r="X65" t="str">
-        <v>nwilson@gmail.com</v>
+        <v>nwilson@example.com</v>
       </c>
       <c r="Y65" t="str">
-        <v>110 W Adams St</v>
+        <v>130 Demo Street</v>
       </c>
       <c r="Z65" t="str">
         <v>Chicago</v>
@@ -24186,7 +24186,7 @@
         <v>SSN</v>
       </c>
       <c r="BD65" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="BF65">
         <v>45523</v>
@@ -24276,7 +24276,7 @@
         <v>Wilson</v>
       </c>
       <c r="CL65" t="str">
-        <v>IL3858215</v>
+        <v>IL0000049</v>
       </c>
       <c r="CM65" t="str">
         <v>IL</v>
@@ -24294,7 +24294,7 @@
         <v>46752</v>
       </c>
       <c r="CR65" t="str">
-        <v>(312) 807-8788</v>
+        <v>(312) 555-0109</v>
       </c>
       <c r="CS65" t="str">
         <v>Dr. Shannon Cole</v>
@@ -24410,22 +24410,22 @@
         <v>Noah Wilson</v>
       </c>
       <c r="C66" t="str">
-        <v>110 W Adams St, Chicago, IL 60603</v>
+        <v>130 Demo Street, Chicago, IL 60603</v>
       </c>
       <c r="D66" t="str">
-        <v>582-987-2387</v>
+        <v>582-555-0100</v>
       </c>
       <c r="E66" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="F66" t="str">
         <v>Chase</v>
       </c>
       <c r="G66">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H66">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I66" t="str">
         <v>Medical Certification</v>
@@ -24434,7 +24434,7 @@
         <v>VALID</v>
       </c>
       <c r="K66" t="str">
-        <v>IL2016981</v>
+        <v>IL0000037</v>
       </c>
       <c r="L66">
         <v>46647</v>
@@ -24461,7 +24461,7 @@
         <v>M</v>
       </c>
       <c r="U66">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V66" t="str">
         <v>DRV-010.png</v>
@@ -24470,10 +24470,10 @@
         <v>Black</v>
       </c>
       <c r="X66" t="str">
-        <v>nwilson@gmail.com</v>
+        <v>nwilson@example.com</v>
       </c>
       <c r="Y66" t="str">
-        <v>110 W Adams St</v>
+        <v>130 Demo Street</v>
       </c>
       <c r="Z66" t="str">
         <v>Chicago</v>
@@ -24548,7 +24548,7 @@
         <v>SSN</v>
       </c>
       <c r="BD66" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="BF66">
         <v>45523</v>
@@ -24638,7 +24638,7 @@
         <v>Wilson</v>
       </c>
       <c r="CL66" t="str">
-        <v>IL3858216</v>
+        <v>IL0000050</v>
       </c>
       <c r="CM66" t="str">
         <v>IL</v>
@@ -24656,7 +24656,7 @@
         <v>46752</v>
       </c>
       <c r="CR66" t="str">
-        <v>(312) 807-8788</v>
+        <v>(312) 555-0109</v>
       </c>
       <c r="CS66" t="str">
         <v>Dr. Shannon Cole</v>
@@ -24772,22 +24772,22 @@
         <v>Noah Wilson</v>
       </c>
       <c r="C67" t="str">
-        <v>110 W Adams St, Chicago, IL 60603</v>
+        <v>130 Demo Street, Chicago, IL 60603</v>
       </c>
       <c r="D67" t="str">
-        <v>582-987-2387</v>
+        <v>582-555-0100</v>
       </c>
       <c r="E67" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="F67" t="str">
         <v>Chase</v>
       </c>
       <c r="G67">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H67">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I67" t="str">
         <v>MVR Background Report</v>
@@ -24796,7 +24796,7 @@
         <v>VALID</v>
       </c>
       <c r="K67" t="str">
-        <v>IL4814730</v>
+        <v>IL0000060</v>
       </c>
       <c r="L67">
         <v>46647</v>
@@ -24823,7 +24823,7 @@
         <v>M</v>
       </c>
       <c r="U67">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V67" t="str">
         <v>DRV-010.png</v>
@@ -24832,10 +24832,10 @@
         <v>Black</v>
       </c>
       <c r="X67" t="str">
-        <v>nwilson@gmail.com</v>
+        <v>nwilson@example.com</v>
       </c>
       <c r="Y67" t="str">
-        <v>110 W Adams St</v>
+        <v>130 Demo Street</v>
       </c>
       <c r="Z67" t="str">
         <v>Chicago</v>
@@ -24910,7 +24910,7 @@
         <v>SSN</v>
       </c>
       <c r="BD67" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="BF67">
         <v>45523</v>
@@ -25000,7 +25000,7 @@
         <v>Wilson</v>
       </c>
       <c r="CL67" t="str">
-        <v>IL3858217</v>
+        <v>IL0000051</v>
       </c>
       <c r="CM67" t="str">
         <v>IL</v>
@@ -25018,7 +25018,7 @@
         <v>46752</v>
       </c>
       <c r="CR67" t="str">
-        <v>(312) 807-8788</v>
+        <v>(312) 555-0109</v>
       </c>
       <c r="CS67" t="str">
         <v>Dr. Shannon Cole</v>
@@ -25134,22 +25134,22 @@
         <v>Noah Wilson</v>
       </c>
       <c r="C68" t="str">
-        <v>110 W Adams St, Chicago, IL 60603</v>
+        <v>130 Demo Street, Chicago, IL 60603</v>
       </c>
       <c r="D68" t="str">
-        <v>582-987-2387</v>
+        <v>582-555-0100</v>
       </c>
       <c r="E68" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="F68" t="str">
         <v>Chase</v>
       </c>
       <c r="G68">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H68">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I68" t="str">
         <v>Driver Application</v>
@@ -25158,7 +25158,7 @@
         <v>VALID</v>
       </c>
       <c r="K68" t="str">
-        <v>IL4355788</v>
+        <v>IL0000059</v>
       </c>
       <c r="L68">
         <v>46647</v>
@@ -25185,7 +25185,7 @@
         <v>M</v>
       </c>
       <c r="U68">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V68" t="str">
         <v>DRV-010.png</v>
@@ -25194,10 +25194,10 @@
         <v>Black</v>
       </c>
       <c r="X68" t="str">
-        <v>nwilson@gmail.com</v>
+        <v>nwilson@example.com</v>
       </c>
       <c r="Y68" t="str">
-        <v>110 W Adams St</v>
+        <v>130 Demo Street</v>
       </c>
       <c r="Z68" t="str">
         <v>Chicago</v>
@@ -25272,7 +25272,7 @@
         <v>SSN</v>
       </c>
       <c r="BD68" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="BF68">
         <v>45523</v>
@@ -25362,7 +25362,7 @@
         <v>Wilson</v>
       </c>
       <c r="CL68" t="str">
-        <v>IL3858218</v>
+        <v>IL0000052</v>
       </c>
       <c r="CM68" t="str">
         <v>IL</v>
@@ -25380,7 +25380,7 @@
         <v>46752</v>
       </c>
       <c r="CR68" t="str">
-        <v>(312) 807-8788</v>
+        <v>(312) 555-0109</v>
       </c>
       <c r="CS68" t="str">
         <v>Dr. Shannon Cole</v>
@@ -25496,22 +25496,22 @@
         <v>Noah Wilson</v>
       </c>
       <c r="C69" t="str">
-        <v>110 W Adams St, Chicago, IL 60603</v>
+        <v>130 Demo Street, Chicago, IL 60603</v>
       </c>
       <c r="D69" t="str">
-        <v>582-987-2387</v>
+        <v>582-555-0100</v>
       </c>
       <c r="E69" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="F69" t="str">
         <v>Chase</v>
       </c>
       <c r="G69">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H69">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I69" t="str">
         <v>Road Test Certificate</v>
@@ -25520,7 +25520,7 @@
         <v>VALID</v>
       </c>
       <c r="K69" t="str">
-        <v>IL6567205</v>
+        <v>IL0000064</v>
       </c>
       <c r="L69">
         <v>46647</v>
@@ -25547,7 +25547,7 @@
         <v>M</v>
       </c>
       <c r="U69">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V69" t="str">
         <v>DRV-010.png</v>
@@ -25556,10 +25556,10 @@
         <v>Black</v>
       </c>
       <c r="X69" t="str">
-        <v>nwilson@gmail.com</v>
+        <v>nwilson@example.com</v>
       </c>
       <c r="Y69" t="str">
-        <v>110 W Adams St</v>
+        <v>130 Demo Street</v>
       </c>
       <c r="Z69" t="str">
         <v>Chicago</v>
@@ -25634,7 +25634,7 @@
         <v>SSN</v>
       </c>
       <c r="BD69" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="BF69">
         <v>45523</v>
@@ -25724,7 +25724,7 @@
         <v>Wilson</v>
       </c>
       <c r="CL69" t="str">
-        <v>IL3858219</v>
+        <v>IL0000053</v>
       </c>
       <c r="CM69" t="str">
         <v>IL</v>
@@ -25742,7 +25742,7 @@
         <v>46752</v>
       </c>
       <c r="CR69" t="str">
-        <v>(312) 807-8788</v>
+        <v>(312) 555-0109</v>
       </c>
       <c r="CS69" t="str">
         <v>Dr. Shannon Cole</v>
@@ -25858,22 +25858,22 @@
         <v>Noah Wilson</v>
       </c>
       <c r="C70" t="str">
-        <v>110 W Adams St, Chicago, IL 60603</v>
+        <v>130 Demo Street, Chicago, IL 60603</v>
       </c>
       <c r="D70" t="str">
-        <v>582-987-2387</v>
+        <v>582-555-0100</v>
       </c>
       <c r="E70" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="F70" t="str">
         <v>Chase</v>
       </c>
       <c r="G70">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H70">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I70" t="str">
         <v>Incident/Accident Report</v>
@@ -25882,7 +25882,7 @@
         <v>VALID</v>
       </c>
       <c r="K70" t="str">
-        <v>IL6135045</v>
+        <v>IL0000063</v>
       </c>
       <c r="L70">
         <v>46647</v>
@@ -25912,7 +25912,7 @@
         <v>M</v>
       </c>
       <c r="U70">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V70" t="str">
         <v>DRV-010.png</v>
@@ -25921,10 +25921,10 @@
         <v>Black</v>
       </c>
       <c r="X70" t="str">
-        <v>nwilson@gmail.com</v>
+        <v>nwilson@example.com</v>
       </c>
       <c r="Y70" t="str">
-        <v>110 W Adams St</v>
+        <v>130 Demo Street</v>
       </c>
       <c r="Z70" t="str">
         <v>Chicago</v>
@@ -25999,7 +25999,7 @@
         <v>SSN</v>
       </c>
       <c r="BD70" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="BF70">
         <v>45523</v>
@@ -26089,7 +26089,7 @@
         <v>Wilson</v>
       </c>
       <c r="CL70" t="str">
-        <v>IL3858220</v>
+        <v>IL0000054</v>
       </c>
       <c r="CM70" t="str">
         <v>IL</v>
@@ -26107,7 +26107,7 @@
         <v>46752</v>
       </c>
       <c r="CR70" t="str">
-        <v>(312) 807-8788</v>
+        <v>(312) 555-0109</v>
       </c>
       <c r="CS70" t="str">
         <v>Dr. Shannon Cole</v>
@@ -26223,22 +26223,22 @@
         <v>Noah Wilson</v>
       </c>
       <c r="C71" t="str">
-        <v>110 W Adams St, Chicago, IL 60603</v>
+        <v>130 Demo Street, Chicago, IL 60603</v>
       </c>
       <c r="D71" t="str">
-        <v>582-987-2387</v>
+        <v>582-555-0100</v>
       </c>
       <c r="E71" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="F71" t="str">
         <v>Chase</v>
       </c>
       <c r="G71">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H71">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I71" t="str">
         <v>Direct Deposit Form</v>
@@ -26247,7 +26247,7 @@
         <v>VALID</v>
       </c>
       <c r="K71" t="str">
-        <v>IL2535912</v>
+        <v>IL0000038</v>
       </c>
       <c r="L71">
         <v>46647</v>
@@ -26274,7 +26274,7 @@
         <v>M</v>
       </c>
       <c r="U71">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V71" t="str">
         <v>DRV-010.png</v>
@@ -26283,10 +26283,10 @@
         <v>Black</v>
       </c>
       <c r="X71" t="str">
-        <v>nwilson@gmail.com</v>
+        <v>nwilson@example.com</v>
       </c>
       <c r="Y71" t="str">
-        <v>110 W Adams St</v>
+        <v>130 Demo Street</v>
       </c>
       <c r="Z71" t="str">
         <v>Chicago</v>
@@ -26361,7 +26361,7 @@
         <v>SSN</v>
       </c>
       <c r="BD71" t="str">
-        <v>***-**-5590</v>
+        <v>***-**-0112</v>
       </c>
       <c r="BF71">
         <v>45523</v>
@@ -26451,7 +26451,7 @@
         <v>Wilson</v>
       </c>
       <c r="CL71" t="str">
-        <v>IL3858221</v>
+        <v>IL0000055</v>
       </c>
       <c r="CM71" t="str">
         <v>IL</v>
@@ -26469,7 +26469,7 @@
         <v>46752</v>
       </c>
       <c r="CR71" t="str">
-        <v>(312) 807-8788</v>
+        <v>(312) 555-0109</v>
       </c>
       <c r="CS71" t="str">
         <v>Dr. Shannon Cole</v>
@@ -26585,22 +26585,22 @@
         <v>Olivia Lee</v>
       </c>
       <c r="C72" t="str">
-        <v>600 Peachtree St, Atlanta, GA 30308</v>
+        <v>900 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D72" t="str">
-        <v>337-857-3607</v>
+        <v>337-555-0100</v>
       </c>
       <c r="E72" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="F72" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G72">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H72">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I72" t="str">
         <v>CDL Summary</v>
@@ -26609,7 +26609,7 @@
         <v>VALID</v>
       </c>
       <c r="K72" t="str">
-        <v>GA8190601</v>
+        <v>GA0000020</v>
       </c>
       <c r="L72">
         <v>46566</v>
@@ -26636,7 +26636,7 @@
         <v>F</v>
       </c>
       <c r="U72">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V72" t="str">
         <v>DRV-011.png</v>
@@ -26645,10 +26645,10 @@
         <v>South Asian</v>
       </c>
       <c r="X72" t="str">
-        <v>olee@hotmail.com</v>
+        <v>olee@example.com</v>
       </c>
       <c r="Y72" t="str">
-        <v>600 Peachtree St</v>
+        <v>900 Demo Street</v>
       </c>
       <c r="Z72" t="str">
         <v>Atlanta</v>
@@ -26723,7 +26723,7 @@
         <v>SSN</v>
       </c>
       <c r="BD72" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="BF72">
         <v>45551</v>
@@ -26813,7 +26813,7 @@
         <v>Lee</v>
       </c>
       <c r="CL72" t="str">
-        <v>GA8190601</v>
+        <v>GA0000020</v>
       </c>
       <c r="CM72" t="str">
         <v>GA</v>
@@ -26831,7 +26831,7 @@
         <v>46499</v>
       </c>
       <c r="CR72" t="str">
-        <v>(404) 231-4428</v>
+        <v>(404) 555-0100</v>
       </c>
       <c r="CS72" t="str">
         <v>Dr. Melissa Tran</v>
@@ -26947,22 +26947,22 @@
         <v>Olivia Lee</v>
       </c>
       <c r="C73" t="str">
-        <v>600 Peachtree St, Atlanta, GA 30308</v>
+        <v>900 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D73" t="str">
-        <v>337-857-3607</v>
+        <v>337-555-0100</v>
       </c>
       <c r="E73" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="F73" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G73">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H73">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I73" t="str">
         <v>Medical Certification</v>
@@ -26971,7 +26971,7 @@
         <v>VALID</v>
       </c>
       <c r="K73" t="str">
-        <v>GA4750278</v>
+        <v>GA0000007</v>
       </c>
       <c r="L73">
         <v>46566</v>
@@ -26998,7 +26998,7 @@
         <v>F</v>
       </c>
       <c r="U73">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V73" t="str">
         <v>DRV-011.png</v>
@@ -27007,10 +27007,10 @@
         <v>South Asian</v>
       </c>
       <c r="X73" t="str">
-        <v>olee@hotmail.com</v>
+        <v>olee@example.com</v>
       </c>
       <c r="Y73" t="str">
-        <v>600 Peachtree St</v>
+        <v>900 Demo Street</v>
       </c>
       <c r="Z73" t="str">
         <v>Atlanta</v>
@@ -27085,7 +27085,7 @@
         <v>SSN</v>
       </c>
       <c r="BD73" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="BF73">
         <v>45551</v>
@@ -27175,7 +27175,7 @@
         <v>Lee</v>
       </c>
       <c r="CL73" t="str">
-        <v>GA8190602</v>
+        <v>GA0000021</v>
       </c>
       <c r="CM73" t="str">
         <v>GA</v>
@@ -27193,7 +27193,7 @@
         <v>46499</v>
       </c>
       <c r="CR73" t="str">
-        <v>(404) 231-4428</v>
+        <v>(404) 555-0100</v>
       </c>
       <c r="CS73" t="str">
         <v>Dr. Melissa Tran</v>
@@ -27309,22 +27309,22 @@
         <v>Olivia Lee</v>
       </c>
       <c r="C74" t="str">
-        <v>600 Peachtree St, Atlanta, GA 30308</v>
+        <v>900 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D74" t="str">
-        <v>337-857-3607</v>
+        <v>337-555-0100</v>
       </c>
       <c r="E74" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="F74" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G74">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H74">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I74" t="str">
         <v>MVR Background Report</v>
@@ -27333,7 +27333,7 @@
         <v>VALID</v>
       </c>
       <c r="K74" t="str">
-        <v>GA5818610</v>
+        <v>GA0000009</v>
       </c>
       <c r="L74">
         <v>46566</v>
@@ -27360,7 +27360,7 @@
         <v>F</v>
       </c>
       <c r="U74">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V74" t="str">
         <v>DRV-011.png</v>
@@ -27369,10 +27369,10 @@
         <v>South Asian</v>
       </c>
       <c r="X74" t="str">
-        <v>olee@hotmail.com</v>
+        <v>olee@example.com</v>
       </c>
       <c r="Y74" t="str">
-        <v>600 Peachtree St</v>
+        <v>900 Demo Street</v>
       </c>
       <c r="Z74" t="str">
         <v>Atlanta</v>
@@ -27447,7 +27447,7 @@
         <v>SSN</v>
       </c>
       <c r="BD74" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="BF74">
         <v>45551</v>
@@ -27537,7 +27537,7 @@
         <v>Lee</v>
       </c>
       <c r="CL74" t="str">
-        <v>GA8190603</v>
+        <v>GA0000022</v>
       </c>
       <c r="CM74" t="str">
         <v>GA</v>
@@ -27555,7 +27555,7 @@
         <v>46499</v>
       </c>
       <c r="CR74" t="str">
-        <v>(404) 231-4428</v>
+        <v>(404) 555-0100</v>
       </c>
       <c r="CS74" t="str">
         <v>Dr. Melissa Tran</v>
@@ -27671,22 +27671,22 @@
         <v>Olivia Lee</v>
       </c>
       <c r="C75" t="str">
-        <v>600 Peachtree St, Atlanta, GA 30308</v>
+        <v>900 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D75" t="str">
-        <v>337-857-3607</v>
+        <v>337-555-0100</v>
       </c>
       <c r="E75" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="F75" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G75">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H75">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I75" t="str">
         <v>Driver Application</v>
@@ -27695,7 +27695,7 @@
         <v>VALID</v>
       </c>
       <c r="K75" t="str">
-        <v>GA5852321</v>
+        <v>GA0000010</v>
       </c>
       <c r="L75">
         <v>46566</v>
@@ -27722,7 +27722,7 @@
         <v>F</v>
       </c>
       <c r="U75">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V75" t="str">
         <v>DRV-011.png</v>
@@ -27731,10 +27731,10 @@
         <v>South Asian</v>
       </c>
       <c r="X75" t="str">
-        <v>olee@hotmail.com</v>
+        <v>olee@example.com</v>
       </c>
       <c r="Y75" t="str">
-        <v>600 Peachtree St</v>
+        <v>900 Demo Street</v>
       </c>
       <c r="Z75" t="str">
         <v>Atlanta</v>
@@ -27809,7 +27809,7 @@
         <v>SSN</v>
       </c>
       <c r="BD75" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="BF75">
         <v>45551</v>
@@ -27899,7 +27899,7 @@
         <v>Lee</v>
       </c>
       <c r="CL75" t="str">
-        <v>GA8190604</v>
+        <v>GA0000023</v>
       </c>
       <c r="CM75" t="str">
         <v>GA</v>
@@ -27917,7 +27917,7 @@
         <v>46499</v>
       </c>
       <c r="CR75" t="str">
-        <v>(404) 231-4428</v>
+        <v>(404) 555-0100</v>
       </c>
       <c r="CS75" t="str">
         <v>Dr. Melissa Tran</v>
@@ -28033,22 +28033,22 @@
         <v>Olivia Lee</v>
       </c>
       <c r="C76" t="str">
-        <v>600 Peachtree St, Atlanta, GA 30308</v>
+        <v>900 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D76" t="str">
-        <v>337-857-3607</v>
+        <v>337-555-0100</v>
       </c>
       <c r="E76" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="F76" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G76">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H76">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I76" t="str">
         <v>Road Test Certificate</v>
@@ -28057,7 +28057,7 @@
         <v>VALID</v>
       </c>
       <c r="K76" t="str">
-        <v>GA6447082</v>
+        <v>GA0000012</v>
       </c>
       <c r="L76">
         <v>46566</v>
@@ -28084,7 +28084,7 @@
         <v>F</v>
       </c>
       <c r="U76">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V76" t="str">
         <v>DRV-011.png</v>
@@ -28093,10 +28093,10 @@
         <v>South Asian</v>
       </c>
       <c r="X76" t="str">
-        <v>olee@hotmail.com</v>
+        <v>olee@example.com</v>
       </c>
       <c r="Y76" t="str">
-        <v>600 Peachtree St</v>
+        <v>900 Demo Street</v>
       </c>
       <c r="Z76" t="str">
         <v>Atlanta</v>
@@ -28171,7 +28171,7 @@
         <v>SSN</v>
       </c>
       <c r="BD76" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="BF76">
         <v>45551</v>
@@ -28261,7 +28261,7 @@
         <v>Lee</v>
       </c>
       <c r="CL76" t="str">
-        <v>GA8190605</v>
+        <v>GA0000024</v>
       </c>
       <c r="CM76" t="str">
         <v>GA</v>
@@ -28279,7 +28279,7 @@
         <v>46499</v>
       </c>
       <c r="CR76" t="str">
-        <v>(404) 231-4428</v>
+        <v>(404) 555-0100</v>
       </c>
       <c r="CS76" t="str">
         <v>Dr. Melissa Tran</v>
@@ -28395,22 +28395,22 @@
         <v>Olivia Lee</v>
       </c>
       <c r="C77" t="str">
-        <v>600 Peachtree St, Atlanta, GA 30308</v>
+        <v>900 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D77" t="str">
-        <v>337-857-3607</v>
+        <v>337-555-0100</v>
       </c>
       <c r="E77" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="F77" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G77">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H77">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I77" t="str">
         <v>Incident/Accident Report</v>
@@ -28419,7 +28419,7 @@
         <v>VALID</v>
       </c>
       <c r="K77" t="str">
-        <v>GA5384195</v>
+        <v>GA0000008</v>
       </c>
       <c r="L77">
         <v>46566</v>
@@ -28449,7 +28449,7 @@
         <v>F</v>
       </c>
       <c r="U77">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V77" t="str">
         <v>DRV-011.png</v>
@@ -28458,10 +28458,10 @@
         <v>South Asian</v>
       </c>
       <c r="X77" t="str">
-        <v>olee@hotmail.com</v>
+        <v>olee@example.com</v>
       </c>
       <c r="Y77" t="str">
-        <v>600 Peachtree St</v>
+        <v>900 Demo Street</v>
       </c>
       <c r="Z77" t="str">
         <v>Atlanta</v>
@@ -28536,7 +28536,7 @@
         <v>SSN</v>
       </c>
       <c r="BD77" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="BF77">
         <v>45551</v>
@@ -28626,7 +28626,7 @@
         <v>Lee</v>
       </c>
       <c r="CL77" t="str">
-        <v>GA8190606</v>
+        <v>GA0000025</v>
       </c>
       <c r="CM77" t="str">
         <v>GA</v>
@@ -28644,7 +28644,7 @@
         <v>46499</v>
       </c>
       <c r="CR77" t="str">
-        <v>(404) 231-4428</v>
+        <v>(404) 555-0100</v>
       </c>
       <c r="CS77" t="str">
         <v>Dr. Melissa Tran</v>
@@ -28760,22 +28760,22 @@
         <v>Olivia Lee</v>
       </c>
       <c r="C78" t="str">
-        <v>600 Peachtree St, Atlanta, GA 30308</v>
+        <v>900 Demo Street, Atlanta, GA 30308</v>
       </c>
       <c r="D78" t="str">
-        <v>337-857-3607</v>
+        <v>337-555-0100</v>
       </c>
       <c r="E78" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="F78" t="str">
         <v>Bank of America</v>
       </c>
       <c r="G78">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H78">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I78" t="str">
         <v>Direct Deposit Form</v>
@@ -28784,7 +28784,7 @@
         <v>VALID</v>
       </c>
       <c r="K78" t="str">
-        <v>GA1861689</v>
+        <v>GA0000003</v>
       </c>
       <c r="L78">
         <v>46566</v>
@@ -28811,7 +28811,7 @@
         <v>F</v>
       </c>
       <c r="U78">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V78" t="str">
         <v>DRV-011.png</v>
@@ -28820,10 +28820,10 @@
         <v>South Asian</v>
       </c>
       <c r="X78" t="str">
-        <v>olee@hotmail.com</v>
+        <v>olee@example.com</v>
       </c>
       <c r="Y78" t="str">
-        <v>600 Peachtree St</v>
+        <v>900 Demo Street</v>
       </c>
       <c r="Z78" t="str">
         <v>Atlanta</v>
@@ -28898,7 +28898,7 @@
         <v>SSN</v>
       </c>
       <c r="BD78" t="str">
-        <v>***-**-5273</v>
+        <v>***-**-0111</v>
       </c>
       <c r="BF78">
         <v>45551</v>
@@ -28988,7 +28988,7 @@
         <v>Lee</v>
       </c>
       <c r="CL78" t="str">
-        <v>GA8190607</v>
+        <v>GA0000026</v>
       </c>
       <c r="CM78" t="str">
         <v>GA</v>
@@ -29006,7 +29006,7 @@
         <v>46499</v>
       </c>
       <c r="CR78" t="str">
-        <v>(404) 231-4428</v>
+        <v>(404) 555-0100</v>
       </c>
       <c r="CS78" t="str">
         <v>Dr. Melissa Tran</v>
@@ -29122,22 +29122,22 @@
         <v>Robert Johnson</v>
       </c>
       <c r="C79" t="str">
-        <v>618 S Michigan Ave, Chicago, IL 60605</v>
+        <v>920 Demo Street, Chicago, IL 60605</v>
       </c>
       <c r="D79" t="str">
-        <v>618-667-2121</v>
+        <v>618-555-0101</v>
       </c>
       <c r="E79" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="F79" t="str">
         <v>Wells Fargo</v>
       </c>
       <c r="G79">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H79">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I79" t="str">
         <v>CDL Summary</v>
@@ -29146,7 +29146,7 @@
         <v>VALID</v>
       </c>
       <c r="K79" t="str">
-        <v>IL1895570</v>
+        <v>IL0000030</v>
       </c>
       <c r="L79">
         <v>46706</v>
@@ -29173,7 +29173,7 @@
         <v>M</v>
       </c>
       <c r="U79">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V79" t="str">
         <v>DRV-012.png</v>
@@ -29182,10 +29182,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X79" t="str">
-        <v>robertjohnson@hotmail.com</v>
+        <v>robertjohnson@example.com</v>
       </c>
       <c r="Y79" t="str">
-        <v>618 S Michigan Ave</v>
+        <v>920 Demo Street</v>
       </c>
       <c r="Z79" t="str">
         <v>Chicago</v>
@@ -29266,7 +29266,7 @@
         <v>SSN</v>
       </c>
       <c r="BD79" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="BF79">
         <v>45579</v>
@@ -29359,7 +29359,7 @@
         <v>Johnson</v>
       </c>
       <c r="CL79" t="str">
-        <v>IL1895570</v>
+        <v>IL0000030</v>
       </c>
       <c r="CM79" t="str">
         <v>IL</v>
@@ -29377,7 +29377,7 @@
         <v>46609</v>
       </c>
       <c r="CR79" t="str">
-        <v>(312) 300-1431</v>
+        <v>(312) 555-0103</v>
       </c>
       <c r="CS79" t="str">
         <v>Dr. Victor Reed</v>
@@ -29493,22 +29493,22 @@
         <v>Robert Johnson</v>
       </c>
       <c r="C80" t="str">
-        <v>618 S Michigan Ave, Chicago, IL 60605</v>
+        <v>920 Demo Street, Chicago, IL 60605</v>
       </c>
       <c r="D80" t="str">
-        <v>618-667-2121</v>
+        <v>618-555-0101</v>
       </c>
       <c r="E80" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="F80" t="str">
         <v>Wells Fargo</v>
       </c>
       <c r="G80">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H80">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I80" t="str">
         <v>Medical Certification</v>
@@ -29517,7 +29517,7 @@
         <v>VALID</v>
       </c>
       <c r="K80" t="str">
-        <v>IL5451183</v>
+        <v>IL0000062</v>
       </c>
       <c r="L80">
         <v>46706</v>
@@ -29544,7 +29544,7 @@
         <v>M</v>
       </c>
       <c r="U80">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V80" t="str">
         <v>DRV-012.png</v>
@@ -29553,10 +29553,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X80" t="str">
-        <v>robertjohnson@hotmail.com</v>
+        <v>robertjohnson@example.com</v>
       </c>
       <c r="Y80" t="str">
-        <v>618 S Michigan Ave</v>
+        <v>920 Demo Street</v>
       </c>
       <c r="Z80" t="str">
         <v>Chicago</v>
@@ -29637,7 +29637,7 @@
         <v>SSN</v>
       </c>
       <c r="BD80" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="BF80">
         <v>45579</v>
@@ -29730,7 +29730,7 @@
         <v>Johnson</v>
       </c>
       <c r="CL80" t="str">
-        <v>IL1895571</v>
+        <v>IL0000031</v>
       </c>
       <c r="CM80" t="str">
         <v>IL</v>
@@ -29748,7 +29748,7 @@
         <v>46609</v>
       </c>
       <c r="CR80" t="str">
-        <v>(312) 300-1431</v>
+        <v>(312) 555-0103</v>
       </c>
       <c r="CS80" t="str">
         <v>Dr. Victor Reed</v>
@@ -29864,22 +29864,22 @@
         <v>Robert Johnson</v>
       </c>
       <c r="C81" t="str">
-        <v>618 S Michigan Ave, Chicago, IL 60605</v>
+        <v>920 Demo Street, Chicago, IL 60605</v>
       </c>
       <c r="D81" t="str">
-        <v>618-667-2121</v>
+        <v>618-555-0101</v>
       </c>
       <c r="E81" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="F81" t="str">
         <v>Wells Fargo</v>
       </c>
       <c r="G81">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H81">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I81" t="str">
         <v>MVR Background Report</v>
@@ -29888,7 +29888,7 @@
         <v>VALID</v>
       </c>
       <c r="K81" t="str">
-        <v>IL2852329</v>
+        <v>IL0000040</v>
       </c>
       <c r="L81">
         <v>46706</v>
@@ -29915,7 +29915,7 @@
         <v>M</v>
       </c>
       <c r="U81">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V81" t="str">
         <v>DRV-012.png</v>
@@ -29924,10 +29924,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X81" t="str">
-        <v>robertjohnson@hotmail.com</v>
+        <v>robertjohnson@example.com</v>
       </c>
       <c r="Y81" t="str">
-        <v>618 S Michigan Ave</v>
+        <v>920 Demo Street</v>
       </c>
       <c r="Z81" t="str">
         <v>Chicago</v>
@@ -30008,7 +30008,7 @@
         <v>SSN</v>
       </c>
       <c r="BD81" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="BF81">
         <v>45579</v>
@@ -30101,7 +30101,7 @@
         <v>Johnson</v>
       </c>
       <c r="CL81" t="str">
-        <v>IL1895572</v>
+        <v>IL0000032</v>
       </c>
       <c r="CM81" t="str">
         <v>IL</v>
@@ -30119,7 +30119,7 @@
         <v>46609</v>
       </c>
       <c r="CR81" t="str">
-        <v>(312) 300-1431</v>
+        <v>(312) 555-0103</v>
       </c>
       <c r="CS81" t="str">
         <v>Dr. Victor Reed</v>
@@ -30235,22 +30235,22 @@
         <v>Robert Johnson</v>
       </c>
       <c r="C82" t="str">
-        <v>618 S Michigan Ave, Chicago, IL 60605</v>
+        <v>920 Demo Street, Chicago, IL 60605</v>
       </c>
       <c r="D82" t="str">
-        <v>618-667-2121</v>
+        <v>618-555-0101</v>
       </c>
       <c r="E82" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="F82" t="str">
         <v>Wells Fargo</v>
       </c>
       <c r="G82">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H82">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I82" t="str">
         <v>Driver Application</v>
@@ -30259,7 +30259,7 @@
         <v>VALID</v>
       </c>
       <c r="K82" t="str">
-        <v>IL4305571</v>
+        <v>IL0000057</v>
       </c>
       <c r="L82">
         <v>46706</v>
@@ -30286,7 +30286,7 @@
         <v>M</v>
       </c>
       <c r="U82">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V82" t="str">
         <v>DRV-012.png</v>
@@ -30295,10 +30295,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X82" t="str">
-        <v>robertjohnson@hotmail.com</v>
+        <v>robertjohnson@example.com</v>
       </c>
       <c r="Y82" t="str">
-        <v>618 S Michigan Ave</v>
+        <v>920 Demo Street</v>
       </c>
       <c r="Z82" t="str">
         <v>Chicago</v>
@@ -30379,7 +30379,7 @@
         <v>SSN</v>
       </c>
       <c r="BD82" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="BF82">
         <v>45579</v>
@@ -30472,7 +30472,7 @@
         <v>Johnson</v>
       </c>
       <c r="CL82" t="str">
-        <v>IL1895573</v>
+        <v>IL0000033</v>
       </c>
       <c r="CM82" t="str">
         <v>IL</v>
@@ -30490,7 +30490,7 @@
         <v>46609</v>
       </c>
       <c r="CR82" t="str">
-        <v>(312) 300-1431</v>
+        <v>(312) 555-0103</v>
       </c>
       <c r="CS82" t="str">
         <v>Dr. Victor Reed</v>
@@ -30606,22 +30606,22 @@
         <v>Robert Johnson</v>
       </c>
       <c r="C83" t="str">
-        <v>618 S Michigan Ave, Chicago, IL 60605</v>
+        <v>920 Demo Street, Chicago, IL 60605</v>
       </c>
       <c r="D83" t="str">
-        <v>618-667-2121</v>
+        <v>618-555-0101</v>
       </c>
       <c r="E83" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="F83" t="str">
         <v>Wells Fargo</v>
       </c>
       <c r="G83">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H83">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I83" t="str">
         <v>Road Test Certificate</v>
@@ -30630,7 +30630,7 @@
         <v>VALID</v>
       </c>
       <c r="K83" t="str">
-        <v>IL8325086</v>
+        <v>IL0000066</v>
       </c>
       <c r="L83">
         <v>46706</v>
@@ -30657,7 +30657,7 @@
         <v>M</v>
       </c>
       <c r="U83">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V83" t="str">
         <v>DRV-012.png</v>
@@ -30666,10 +30666,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X83" t="str">
-        <v>robertjohnson@hotmail.com</v>
+        <v>robertjohnson@example.com</v>
       </c>
       <c r="Y83" t="str">
-        <v>618 S Michigan Ave</v>
+        <v>920 Demo Street</v>
       </c>
       <c r="Z83" t="str">
         <v>Chicago</v>
@@ -30750,7 +30750,7 @@
         <v>SSN</v>
       </c>
       <c r="BD83" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="BF83">
         <v>45579</v>
@@ -30843,7 +30843,7 @@
         <v>Johnson</v>
       </c>
       <c r="CL83" t="str">
-        <v>IL1895574</v>
+        <v>IL0000034</v>
       </c>
       <c r="CM83" t="str">
         <v>IL</v>
@@ -30861,7 +30861,7 @@
         <v>46609</v>
       </c>
       <c r="CR83" t="str">
-        <v>(312) 300-1431</v>
+        <v>(312) 555-0103</v>
       </c>
       <c r="CS83" t="str">
         <v>Dr. Victor Reed</v>
@@ -30977,22 +30977,22 @@
         <v>Robert Johnson</v>
       </c>
       <c r="C84" t="str">
-        <v>618 S Michigan Ave, Chicago, IL 60605</v>
+        <v>920 Demo Street, Chicago, IL 60605</v>
       </c>
       <c r="D84" t="str">
-        <v>618-667-2121</v>
+        <v>618-555-0101</v>
       </c>
       <c r="E84" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="F84" t="str">
         <v>Wells Fargo</v>
       </c>
       <c r="G84">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H84">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I84" t="str">
         <v>Incident/Accident Report</v>
@@ -31001,7 +31001,7 @@
         <v>VALID</v>
       </c>
       <c r="K84" t="str">
-        <v>IL3423206</v>
+        <v>IL0000048</v>
       </c>
       <c r="L84">
         <v>46706</v>
@@ -31031,7 +31031,7 @@
         <v>M</v>
       </c>
       <c r="U84">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V84" t="str">
         <v>DRV-012.png</v>
@@ -31040,10 +31040,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X84" t="str">
-        <v>robertjohnson@hotmail.com</v>
+        <v>robertjohnson@example.com</v>
       </c>
       <c r="Y84" t="str">
-        <v>618 S Michigan Ave</v>
+        <v>920 Demo Street</v>
       </c>
       <c r="Z84" t="str">
         <v>Chicago</v>
@@ -31124,7 +31124,7 @@
         <v>SSN</v>
       </c>
       <c r="BD84" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="BF84">
         <v>45579</v>
@@ -31217,7 +31217,7 @@
         <v>Johnson</v>
       </c>
       <c r="CL84" t="str">
-        <v>IL1895575</v>
+        <v>IL0000035</v>
       </c>
       <c r="CM84" t="str">
         <v>IL</v>
@@ -31235,7 +31235,7 @@
         <v>46609</v>
       </c>
       <c r="CR84" t="str">
-        <v>(312) 300-1431</v>
+        <v>(312) 555-0103</v>
       </c>
       <c r="CS84" t="str">
         <v>Dr. Victor Reed</v>
@@ -31351,22 +31351,22 @@
         <v>Robert Johnson</v>
       </c>
       <c r="C85" t="str">
-        <v>618 S Michigan Ave, Chicago, IL 60605</v>
+        <v>920 Demo Street, Chicago, IL 60605</v>
       </c>
       <c r="D85" t="str">
-        <v>618-667-2121</v>
+        <v>618-555-0101</v>
       </c>
       <c r="E85" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="F85" t="str">
         <v>Wells Fargo</v>
       </c>
       <c r="G85">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H85">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I85" t="str">
         <v>Direct Deposit Form</v>
@@ -31375,7 +31375,7 @@
         <v>VALID</v>
       </c>
       <c r="K85" t="str">
-        <v>IL2655126</v>
+        <v>IL0000039</v>
       </c>
       <c r="L85">
         <v>46706</v>
@@ -31402,7 +31402,7 @@
         <v>M</v>
       </c>
       <c r="U85">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V85" t="str">
         <v>DRV-012.png</v>
@@ -31411,10 +31411,10 @@
         <v>Caucasian</v>
       </c>
       <c r="X85" t="str">
-        <v>robertjohnson@hotmail.com</v>
+        <v>robertjohnson@example.com</v>
       </c>
       <c r="Y85" t="str">
-        <v>618 S Michigan Ave</v>
+        <v>920 Demo Street</v>
       </c>
       <c r="Z85" t="str">
         <v>Chicago</v>
@@ -31495,7 +31495,7 @@
         <v>SSN</v>
       </c>
       <c r="BD85" t="str">
-        <v>***-**-5664</v>
+        <v>***-**-0114</v>
       </c>
       <c r="BF85">
         <v>45579</v>
@@ -31588,7 +31588,7 @@
         <v>Johnson</v>
       </c>
       <c r="CL85" t="str">
-        <v>IL1895576</v>
+        <v>IL0000036</v>
       </c>
       <c r="CM85" t="str">
         <v>IL</v>
@@ -31606,7 +31606,7 @@
         <v>46609</v>
       </c>
       <c r="CR85" t="str">
-        <v>(312) 300-1431</v>
+        <v>(312) 555-0103</v>
       </c>
       <c r="CS85" t="str">
         <v>Dr. Victor Reed</v>
@@ -31716,7 +31716,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>DRV-001    322-40-9443</v>
+        <v>DRV-001    900-00-0123</v>
       </c>
       <c r="D87" t="str">
         <v>John T. Carter</v>
@@ -31724,7 +31724,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>DRV-002    164-67-3407</v>
+        <v>DRV-002    900-00-0105</v>
       </c>
       <c r="D88" t="str">
         <v>Maria E. Lopez</v>
@@ -31732,7 +31732,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>DRV-003    997-32-7047</v>
+        <v>DRV-003    900-00-0116</v>
       </c>
       <c r="D89" t="str">
         <v>Alex J. Kim</v>
@@ -31740,7 +31740,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>DRV-004    136-33-8257</v>
+        <v>DRV-004    900-00-0119</v>
       </c>
       <c r="D90" t="str">
         <v>Priya A. Patel</v>
@@ -31748,7 +31748,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>DRV-005    438-27-1789</v>
+        <v>DRV-005    900-00-0102</v>
       </c>
       <c r="D91" t="str">
         <v>Kenji H. Tanaka</v>
@@ -31756,7 +31756,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>DRV-006    121-25-1521</v>
+        <v>DRV-006    900-00-0101</v>
       </c>
       <c r="D92" t="str">
         <v>Marcus W. Chen</v>
@@ -31764,7 +31764,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>DRV-007    560-64-4815</v>
+        <v>DRV-007    900-00-0109</v>
       </c>
       <c r="D93" t="str">
         <v>Sofia I. Gomez</v>
@@ -31772,7 +31772,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>DRV-008    441-80-4800</v>
+        <v>DRV-008    900-00-0108</v>
       </c>
       <c r="D94" t="str">
         <v>Liam P. Smith</v>
@@ -31780,7 +31780,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>DRV-009    876-90-9930</v>
+        <v>DRV-009    900-00-0124</v>
       </c>
       <c r="D95" t="str">
         <v>Emma C. Brown</v>
@@ -31788,7 +31788,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>DRV-010    609-69-5590</v>
+        <v>DRV-010    900-00-0112</v>
       </c>
       <c r="D96" t="str">
         <v>Noah R. Wilson</v>
@@ -31796,7 +31796,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>DRV-011    389-76-5273</v>
+        <v>DRV-011    900-00-0111</v>
       </c>
       <c r="D97" t="str">
         <v>Olivia M. Lee</v>
@@ -31804,7 +31804,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>DRV-012    815-21-5664</v>
+        <v>DRV-012    900-00-0114</v>
       </c>
       <c r="D98" t="str">
         <v>Robert D. Johnson</v>
